--- a/api/templates/genxpert_tb_workload_report/uk.xlsx
+++ b/api/templates/genxpert_tb_workload_report/uk.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="25629"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26026"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu-18.04\home\nsabaj\Repositories\aspect\api\templates\device_report\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl$\ubuntu\home\ahernandez\repos\aspect\api\templates\genxpert_tb_workload_report\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0AEE26AC-C6DA-4E32-BF7C-1AE56613DE14}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{123666AA-145F-4000-8D69-C13B35621A98}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-60" windowWidth="29040" windowHeight="15720" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="24" yWindow="24" windowWidth="23016" windowHeight="12936" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Devices" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="64">
   <si>
     <t>Пристрої GeneXpert</t>
   </si>
@@ -206,9 +206,6 @@
     <t>&lt;reasonForInterruption&gt;</t>
   </si>
   <si>
-    <t>&lt;totalXpertTests&gt;</t>
-  </si>
-  <si>
     <t># MTB траса</t>
   </si>
   <si>
@@ -216,6 +213,21 @@
   </si>
   <si>
     <t># MTB+ Стійкий до RIF</t>
+  </si>
+  <si>
+    <t>&lt;lastResultUploadedOn&gt;</t>
+  </si>
+  <si>
+    <t>&lt;lastResultConductedOn&gt;</t>
+  </si>
+  <si>
+    <t>&lt;totalXpertResults&gt;</t>
+  </si>
+  <si>
+    <t>Останній результат завантажено на</t>
+  </si>
+  <si>
+    <t>Останній результат проведено на</t>
   </si>
 </sst>
 </file>
@@ -225,7 +237,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd\ hh:mm"/>
   </numFmts>
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color rgb="FF000000"/>
@@ -258,6 +270,14 @@
     </font>
     <font>
       <b/>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <u/>
       <sz val="12"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
@@ -321,8 +341,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -331,9 +350,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -356,6 +372,11 @@
     </xf>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -738,7 +759,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AA14"/>
+  <dimension ref="A1:AC14"/>
   <sheetFormatPr defaultColWidth="11.296875" defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="27.19921875" customWidth="1"/>
@@ -751,246 +772,264 @@
     <col min="14" max="14" width="13.59765625" customWidth="1"/>
     <col min="15" max="21" width="15.59765625" customWidth="1"/>
     <col min="22" max="23" width="20.59765625" customWidth="1"/>
-    <col min="24" max="25" width="20.59765625" style="2" customWidth="1"/>
+    <col min="24" max="25" width="20.59765625" style="1" customWidth="1"/>
     <col min="26" max="26" width="33.296875" customWidth="1"/>
-    <col min="27" max="27" width="20.59765625" customWidth="1"/>
+    <col min="27" max="27" width="32.8984375" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="31.09765625" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="20.59765625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:27" ht="21" x14ac:dyDescent="0.4">
-      <c r="A1" s="3" t="s">
+    <row r="1" spans="1:29" ht="21" x14ac:dyDescent="0.4">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="3"/>
-      <c r="D1" s="3"/>
-      <c r="E1" s="3"/>
-    </row>
-    <row r="2" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="C1" s="2"/>
+      <c r="D1" s="2"/>
+      <c r="E1" s="2"/>
+    </row>
+    <row r="2" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>1</v>
       </c>
-      <c r="C2" t="s">
+      <c r="C2" s="18" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>3</v>
       </c>
-      <c r="C3" s="1" t="s">
+      <c r="C3" s="16" t="s">
         <v>4</v>
       </c>
-      <c r="D3" s="1"/>
-    </row>
-    <row r="4" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="D3" s="16"/>
+    </row>
+    <row r="4" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="5" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="A5" s="4" t="s">
+    <row r="5" spans="1:29" x14ac:dyDescent="0.3">
+      <c r="A5" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C5" t="s">
+      <c r="C5" s="18" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="6" spans="1:27" ht="78" x14ac:dyDescent="0.3">
-      <c r="C6" s="5" t="s">
+    <row r="6" spans="1:29" ht="47.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C6" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="D6" s="6" t="s">
+      <c r="D6" s="17" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="7" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="A7" s="7"/>
-    </row>
-    <row r="8" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="A8" s="8"/>
-    </row>
-    <row r="9" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="E6" s="17"/>
+      <c r="F6" s="17"/>
+      <c r="G6" s="17"/>
+    </row>
+    <row r="7" spans="1:29" x14ac:dyDescent="0.3">
+      <c r="A7" s="5"/>
+    </row>
+    <row r="8" spans="1:29" x14ac:dyDescent="0.3">
+      <c r="A8" s="6"/>
+    </row>
+    <row r="9" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="10" spans="1:27" s="12" customFormat="1" ht="46.8" x14ac:dyDescent="0.3">
-      <c r="A10" s="9" t="s">
+    <row r="10" spans="1:29" s="10" customFormat="1" ht="46.8" x14ac:dyDescent="0.3">
+      <c r="A10" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="B10" s="9" t="s">
+      <c r="B10" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="C10" s="9" t="s">
+      <c r="C10" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="D10" s="9" t="s">
+      <c r="D10" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="E10" s="9" t="s">
+      <c r="E10" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="F10" s="9" t="s">
+      <c r="F10" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="G10" s="9" t="s">
+      <c r="G10" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="H10" s="9" t="s">
+      <c r="H10" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="I10" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="J10" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="K10" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="L10" s="8" t="s">
         <v>57</v>
       </c>
-      <c r="I10" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="J10" s="9" t="s">
-        <v>19</v>
-      </c>
-      <c r="K10" s="9" t="s">
-        <v>19</v>
-      </c>
-      <c r="L10" s="10" t="s">
+      <c r="M10" s="8" t="s">
         <v>58</v>
       </c>
-      <c r="M10" s="10" t="s">
-        <v>59</v>
-      </c>
-      <c r="N10" s="9" t="s">
+      <c r="N10" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="O10" s="9" t="s">
+      <c r="O10" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="P10" s="9" t="s">
+      <c r="P10" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="Q10" s="9" t="s">
+      <c r="Q10" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="R10" s="9" t="s">
+      <c r="R10" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="S10" s="9" t="s">
+      <c r="S10" s="7" t="s">
         <v>25</v>
       </c>
-      <c r="T10" s="9" t="s">
+      <c r="T10" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="U10" s="10" t="s">
+      <c r="U10" s="8" t="s">
         <v>27</v>
       </c>
-      <c r="V10" s="10" t="s">
+      <c r="V10" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="W10" s="9" t="s">
+      <c r="W10" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="X10" s="11" t="s">
+      <c r="X10" s="9" t="s">
         <v>29</v>
       </c>
-      <c r="Y10" s="11" t="s">
+      <c r="Y10" s="9" t="s">
         <v>30</v>
       </c>
-      <c r="Z10" s="9" t="s">
+      <c r="Z10" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="AA10" s="9" t="s">
+      <c r="AA10" s="7" t="s">
+        <v>62</v>
+      </c>
+      <c r="AB10" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="AC10" s="7" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="11" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="A11" s="13" t="s">
+    <row r="11" spans="1:29" x14ac:dyDescent="0.3">
+      <c r="A11" s="11" t="s">
         <v>33</v>
       </c>
-      <c r="B11" s="13" t="s">
+      <c r="B11" s="11" t="s">
         <v>34</v>
       </c>
-      <c r="C11" s="13" t="s">
+      <c r="C11" s="11" t="s">
         <v>35</v>
       </c>
-      <c r="D11" s="13" t="s">
+      <c r="D11" s="11" t="s">
         <v>36</v>
       </c>
-      <c r="E11" s="13" t="s">
+      <c r="E11" s="11" t="s">
         <v>37</v>
       </c>
-      <c r="F11" s="13" t="s">
+      <c r="F11" s="11" t="s">
         <v>38</v>
       </c>
-      <c r="G11" s="13" t="s">
+      <c r="G11" s="11" t="s">
         <v>39</v>
       </c>
-      <c r="H11" s="13" t="s">
+      <c r="H11" s="11" t="s">
         <v>40</v>
       </c>
-      <c r="I11" s="14" t="s">
+      <c r="I11" s="12" t="s">
         <v>41</v>
       </c>
-      <c r="J11" s="14" t="s">
+      <c r="J11" s="12" t="s">
         <v>42</v>
       </c>
-      <c r="K11" s="14" t="s">
+      <c r="K11" s="12" t="s">
         <v>43</v>
       </c>
-      <c r="L11" s="13" t="s">
+      <c r="L11" s="11" t="s">
         <v>44</v>
       </c>
-      <c r="M11" s="13" t="s">
+      <c r="M11" s="11" t="s">
         <v>45</v>
       </c>
-      <c r="N11" s="13" t="s">
+      <c r="N11" s="11" t="s">
         <v>46</v>
       </c>
-      <c r="O11" s="14" t="s">
+      <c r="O11" s="12" t="s">
         <v>47</v>
       </c>
-      <c r="P11" s="14" t="s">
+      <c r="P11" s="12" t="s">
         <v>48</v>
       </c>
-      <c r="Q11" s="14" t="s">
+      <c r="Q11" s="12" t="s">
         <v>49</v>
       </c>
-      <c r="R11" s="14" t="s">
+      <c r="R11" s="12" t="s">
         <v>50</v>
       </c>
-      <c r="S11" s="14" t="s">
+      <c r="S11" s="12" t="s">
         <v>51</v>
       </c>
-      <c r="T11" s="14" t="s">
+      <c r="T11" s="12" t="s">
         <v>52</v>
       </c>
-      <c r="U11" s="13" t="s">
+      <c r="U11" s="11" t="s">
         <v>53</v>
       </c>
-      <c r="V11" s="13" t="s">
+      <c r="V11" s="11" t="s">
         <v>54</v>
       </c>
-      <c r="W11" s="13" t="s">
+      <c r="W11" s="11" t="s">
         <v>55</v>
       </c>
-      <c r="X11" s="15" t="e">
-        <f>IF(AA11=0,0,I11/AA11)</f>
+      <c r="X11" s="13" t="e">
+        <f>IF(AC11=0,0,I11/AC11)</f>
         <v>#VALUE!</v>
       </c>
-      <c r="Y11" s="16" t="e">
-        <f>IF(AA11=0,0,(I11+J11)/AA11)</f>
+      <c r="Y11" s="14" t="e">
+        <f>IF(AC11=0,0,(I11+J11)/AC11)</f>
         <v>#VALUE!</v>
       </c>
-      <c r="Z11" s="16" t="e">
+      <c r="Z11" s="14" t="e">
         <f>IF(Y11&gt;0.05,"Високий рівень помилок/недійсних даних. Звертайтесь до лаб.","")</f>
         <v>#VALUE!</v>
       </c>
-      <c r="AA11" s="13" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="14" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="B14" s="17"/>
-      <c r="C14" s="17"/>
-      <c r="D14" s="17"/>
-      <c r="E14" s="17"/>
+      <c r="AA11" s="14" t="s">
+        <v>59</v>
+      </c>
+      <c r="AB11" s="14" t="s">
+        <v>60</v>
+      </c>
+      <c r="AC11" s="11" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="14" spans="1:29" x14ac:dyDescent="0.3">
+      <c r="B14" s="15"/>
+      <c r="C14" s="15"/>
+      <c r="D14" s="15"/>
+      <c r="E14" s="15"/>
     </row>
   </sheetData>
-  <mergeCells count="1">
+  <mergeCells count="2">
     <mergeCell ref="C3:D3"/>
+    <mergeCell ref="D6:G6"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300"/>

--- a/api/templates/genxpert_tb_workload_report/uk.xlsx
+++ b/api/templates/genxpert_tb_workload_report/uk.xlsx
@@ -1,48 +1,68 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10309"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ahernandez/repos/aspect/api/templates/genxpert_tb_workload_report/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{32563A87-7BA4-364A-8E12-9B5AD0E0FCFB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="360" yWindow="15" windowWidth="20955" windowHeight="9720" activeTab="0"/>
+    <workbookView xWindow="0" yWindow="760" windowWidth="34560" windowHeight="21580" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Devices" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Пристрої" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr iterateDelta="0.0001"/>
+  <calcPr calcId="191029" iterateDelta="1E-4"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="93">
-  <si>
-    <t xml:space="preserve">Пристрої GeneXpert</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Дати: &lt;Dates&gt;</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="93">
+  <si>
+    <t>Пристрої GeneXpert</t>
+  </si>
+  <si>
+    <t>Дати: &lt;Dates&gt;</t>
   </si>
   <si>
     <t>Примітки</t>
   </si>
   <si>
-    <t xml:space="preserve">Області: &lt;States&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Зверніть увагу, що цей звіт містить результати MTB/Rif, MTB ULTRA та MTB XDR</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Райони: &lt;Lgas&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Сайти: &lt;Sites&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Список літератури</t>
-  </si>
-  <si>
-    <t xml:space="preserve"># Використовувані модулі</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Підраховує кількість днів, коли пристрій принаймні один раз повідомлялося про будь-який із статусів неактивності (включно зі статусами «Невідомо» та «Тестування не проводилися»).</t>
+    <t>Області: &lt;States&gt;</t>
+  </si>
+  <si>
+    <t>Зверніть увагу, що цей звіт містить результати MTB/Rif, MTB ULTRA та MTB XDR</t>
+  </si>
+  <si>
+    <t>Райони: &lt;Lgas&gt;</t>
+  </si>
+  <si>
+    <t>Сайти: &lt;Sites&gt;</t>
+  </si>
+  <si>
+    <t>Список літератури</t>
+  </si>
+  <si>
+    <t># Використовувані модулі</t>
+  </si>
+  <si>
+    <t>Підраховує кількість днів, коли пристрій принаймні один раз повідомлялося про будь-який із статусів неактивності (включно зі статусами «Невідомо» та «Тестування не проводилися»).</t>
   </si>
   <si>
     <t>&lt;Table&gt;</t>
@@ -51,7 +71,7 @@
     <t>пристрій</t>
   </si>
   <si>
-    <t xml:space="preserve">Назва сайту</t>
+    <t>Назва сайту</t>
   </si>
   <si>
     <t>Держава</t>
@@ -63,112 +83,112 @@
     <t>Серійний</t>
   </si>
   <si>
-    <t xml:space="preserve">Серійний номер інструменту</t>
+    <t>Серійний номер інструменту</t>
   </si>
   <si>
     <t>Cтатус</t>
   </si>
   <si>
-    <t xml:space="preserve">Примітка про статус</t>
-  </si>
-  <si>
-    <t xml:space="preserve"># MTB-</t>
-  </si>
-  <si>
-    <t xml:space="preserve"># MTB+</t>
-  </si>
-  <si>
-    <t xml:space="preserve"># MTB траса</t>
-  </si>
-  <si>
-    <t xml:space="preserve"># Помилка MTB</t>
-  </si>
-  <si>
-    <t xml:space="preserve"># MTB Недійсний</t>
-  </si>
-  <si>
-    <t xml:space="preserve"># MTB+ RIF чутливість</t>
-  </si>
-  <si>
-    <t xml:space="preserve"># MTB+ Стійкий до RIF</t>
-  </si>
-  <si>
-    <t xml:space="preserve"># MTB+ RIF невизначений</t>
-  </si>
-  <si>
-    <t xml:space="preserve"># INH</t>
-  </si>
-  <si>
-    <t xml:space="preserve"># FLQ</t>
-  </si>
-  <si>
-    <t xml:space="preserve"># AMK</t>
-  </si>
-  <si>
-    <t xml:space="preserve"># KAN</t>
-  </si>
-  <si>
-    <t xml:space="preserve"># CAP</t>
-  </si>
-  <si>
-    <t xml:space="preserve"># ETH</t>
-  </si>
-  <si>
-    <t xml:space="preserve"># Модулі, використані в діапазоні дат</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Останній пінґ від</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Частота помилок</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Помилка/недійсний показник</t>
+    <t>Примітка про статус</t>
+  </si>
+  <si>
+    <t># MTB-</t>
+  </si>
+  <si>
+    <t># MTB+</t>
+  </si>
+  <si>
+    <t># MTB траса</t>
+  </si>
+  <si>
+    <t># Помилка MTB</t>
+  </si>
+  <si>
+    <t># MTB Недійсний</t>
+  </si>
+  <si>
+    <t># MTB+ RIF чутливість</t>
+  </si>
+  <si>
+    <t># MTB+ Стійкий до RIF</t>
+  </si>
+  <si>
+    <t># MTB+ RIF невизначений</t>
+  </si>
+  <si>
+    <t># INH</t>
+  </si>
+  <si>
+    <t># FLQ</t>
+  </si>
+  <si>
+    <t># AMK</t>
+  </si>
+  <si>
+    <t># KAN</t>
+  </si>
+  <si>
+    <t># CAP</t>
+  </si>
+  <si>
+    <t># ETH</t>
+  </si>
+  <si>
+    <t># Модулі, використані в діапазоні дат</t>
+  </si>
+  <si>
+    <t>Останній пінґ від</t>
+  </si>
+  <si>
+    <t>Частота помилок</t>
+  </si>
+  <si>
+    <t>Помилка/недійсний показник</t>
   </si>
   <si>
     <t>коментар</t>
   </si>
   <si>
-    <t xml:space="preserve">Останній результат завантажено на</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Останній результат проведено на</t>
-  </si>
-  <si>
-    <t xml:space="preserve"># Всього тестів</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Інформація нижче станом на</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Операційна система</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Часовий пояс</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Мова / регіон</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Версія GxConnect</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Пристрій знайдено?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LIS налаштовано правильно?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Дата встановлення GeneXpert</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Номер маршрутизатора</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Реєстраційний номер SIM-карти №1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Реєстраційний номер SIM-карти №2</t>
+    <t>Останній результат завантажено на</t>
+  </si>
+  <si>
+    <t>Останній результат проведено на</t>
+  </si>
+  <si>
+    <t># Всього тестів</t>
+  </si>
+  <si>
+    <t>Інформація нижче станом на</t>
+  </si>
+  <si>
+    <t>Операційна система</t>
+  </si>
+  <si>
+    <t>Часовий пояс</t>
+  </si>
+  <si>
+    <t>Мова / регіон</t>
+  </si>
+  <si>
+    <t>Версія GxConnect</t>
+  </si>
+  <si>
+    <t>Пристрій знайдено?</t>
+  </si>
+  <si>
+    <t>LIS налаштовано правильно?</t>
+  </si>
+  <si>
+    <t>Дата встановлення GeneXpert</t>
+  </si>
+  <si>
+    <t>Номер маршрутизатора</t>
+  </si>
+  <si>
+    <t>Реєстраційний номер SIM-карти №1</t>
+  </si>
+  <si>
+    <t>Реєстраційний номер SIM-карти №2</t>
   </si>
   <si>
     <t>&lt;name&gt;</t>
@@ -297,51 +317,62 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <numFmts count="2">
-    <numFmt numFmtId="160" formatCode="yyyy\-mm\-dd\ hh:mm"/>
-    <numFmt numFmtId="161" formatCode="[$-409]mmmm\ d\,\ yyyy;@"/>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd\ hh:mm"/>
   </numFmts>
-  <fonts count="7">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
-      <sz val="12.000000"/>
+      <sz val="12"/>
       <color indexed="64"/>
       <name val="Calibri"/>
     </font>
     <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
-      <sz val="16.000000"/>
+      <sz val="16"/>
       <color indexed="64"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <u/>
-      <sz val="12.000000"/>
+      <sz val="12"/>
       <color indexed="64"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <i/>
-      <sz val="12.000000"/>
+      <sz val="12"/>
       <color indexed="64"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
-      <sz val="12.000000"/>
+      <sz val="12"/>
       <color indexed="64"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
-      <sz val="12.000000"/>
+      <sz val="12"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
-      <sz val="12.000000"/>
-      <color theme="1"/>
+      <sz val="12"/>
+      <color indexed="64"/>
       <name val="Calibri"/>
-      <scheme val="minor"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="3">
@@ -358,13 +389,13 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="6">
+  <borders count="3">
     <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
     </border>
     <border>
       <left style="medium">
@@ -379,46 +410,7 @@
       <bottom style="medium">
         <color auto="1"/>
       </bottom>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="medium">
-        <color auto="1"/>
-      </left>
-      <right style="medium">
-        <color auto="1"/>
-      </right>
-      <top style="medium">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="medium">
-        <color auto="1"/>
-      </left>
-      <right style="medium">
-        <color auto="1"/>
-      </right>
-      <top style="medium">
-        <color auto="1"/>
-      </top>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="medium">
-        <color auto="1"/>
-      </left>
-      <right style="none"/>
-      <top style="medium">
-        <color auto="1"/>
-      </top>
-      <bottom style="none"/>
-      <diagonal style="none"/>
+      <diagonal/>
     </border>
     <border>
       <left style="thin">
@@ -427,66 +419,73 @@
       <right style="thin">
         <color auto="1"/>
       </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
+      <top/>
       <bottom style="thin">
         <color auto="1"/>
       </bottom>
-      <diagonal style="none"/>
+      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="27">
-    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0"/>
-    <xf fontId="0" fillId="0" borderId="0" numFmtId="10" xfId="0" applyNumberFormat="1"/>
-    <xf fontId="1" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf fontId="1" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf fontId="2" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0"/>
-    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" applyAlignment="1">
+  <cellXfs count="26">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="6" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="10" fontId="6" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf fontId="3" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf fontId="3" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf fontId="4" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf fontId="5" fillId="2" borderId="1" numFmtId="160" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf fontId="5" fillId="2" borderId="1" numFmtId="160" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf fontId="5" fillId="2" borderId="2" numFmtId="160" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf fontId="5" fillId="2" borderId="1" numFmtId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf fontId="5" fillId="2" borderId="3" numFmtId="160" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf fontId="5" fillId="2" borderId="4" numFmtId="160" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf fontId="0" fillId="0" borderId="5" numFmtId="0" xfId="0" applyBorder="1"/>
-    <xf fontId="0" fillId="0" borderId="5" numFmtId="0" xfId="0" applyBorder="1"/>
-    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="14" fontId="7" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf fontId="0" fillId="0" borderId="0" numFmtId="10" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="10" fontId="7" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf fontId="0" fillId="0" borderId="5" numFmtId="10" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf fontId="6" fillId="0" borderId="5" numFmtId="161" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="10" fontId="7" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf fontId="6" fillId="0" borderId="5" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf fontId="4" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf fontId="4" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -497,295 +496,15 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
     </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
   </extLst>
 </styleSheet>
 </file>
 
-<file path=xl/theme/theme.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
-  <a:themeElements>
-    <a:clrScheme name="Office">
-      <a:dk1>
-        <a:sysClr val="windowText" lastClr="000000"/>
-      </a:dk1>
-      <a:lt1>
-        <a:sysClr val="window" lastClr="FFFFFF"/>
-      </a:lt1>
-      <a:dk2>
-        <a:srgbClr val="1F497D"/>
-      </a:dk2>
-      <a:lt2>
-        <a:srgbClr val="EEECE1"/>
-      </a:lt2>
-      <a:accent1>
-        <a:srgbClr val="4F81BD"/>
-      </a:accent1>
-      <a:accent2>
-        <a:srgbClr val="C0504D"/>
-      </a:accent2>
-      <a:accent3>
-        <a:srgbClr val="9BBB59"/>
-      </a:accent3>
-      <a:accent4>
-        <a:srgbClr val="8064A2"/>
-      </a:accent4>
-      <a:accent5>
-        <a:srgbClr val="4BACC6"/>
-      </a:accent5>
-      <a:accent6>
-        <a:srgbClr val="F79646"/>
-      </a:accent6>
-      <a:hlink>
-        <a:srgbClr val="0000FF"/>
-      </a:hlink>
-      <a:folHlink>
-        <a:srgbClr val="800080"/>
-      </a:folHlink>
-    </a:clrScheme>
-    <a:fontScheme name="Office">
-      <a:majorFont>
-        <a:latin typeface="Cambria"/>
-        <a:ea typeface=""/>
-        <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ ゴシック"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
-        <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Times New Roman"/>
-        <a:font script="Hebr" typeface="Times New Roman"/>
-        <a:font script="Thai" typeface="Angsana New"/>
-        <a:font script="Ethi" typeface="Nyala"/>
-        <a:font script="Beng" typeface="Vrinda"/>
-        <a:font script="Gujr" typeface="Shruti"/>
-        <a:font script="Khmr" typeface="MoolBoran"/>
-        <a:font script="Knda" typeface="Tunga"/>
-        <a:font script="Guru" typeface="Raavi"/>
-        <a:font script="Cans" typeface="Euphemia"/>
-        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
-        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
-        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
-        <a:font script="Thaa" typeface="MV Boli"/>
-        <a:font script="Deva" typeface="Mangal"/>
-        <a:font script="Telu" typeface="Gautami"/>
-        <a:font script="Taml" typeface="Latha"/>
-        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
-        <a:font script="Orya" typeface="Kalinga"/>
-        <a:font script="Mlym" typeface="Kartika"/>
-        <a:font script="Laoo" typeface="DokChampa"/>
-        <a:font script="Sinh" typeface="Iskoola Pota"/>
-        <a:font script="Mong" typeface="Mongolian Baiti"/>
-        <a:font script="Viet" typeface="Times New Roman"/>
-        <a:font script="Uigh" typeface="Microsoft Uighur"/>
-      </a:majorFont>
-      <a:minorFont>
-        <a:latin typeface="Calibri"/>
-        <a:ea typeface=""/>
-        <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ 明朝"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
-        <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Arial"/>
-        <a:font script="Hebr" typeface="Arial"/>
-        <a:font script="Thai" typeface="Cordia New"/>
-        <a:font script="Ethi" typeface="Nyala"/>
-        <a:font script="Beng" typeface="Vrinda"/>
-        <a:font script="Gujr" typeface="Shruti"/>
-        <a:font script="Khmr" typeface="DaunPenh"/>
-        <a:font script="Knda" typeface="Tunga"/>
-        <a:font script="Guru" typeface="Raavi"/>
-        <a:font script="Cans" typeface="Euphemia"/>
-        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
-        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
-        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
-        <a:font script="Thaa" typeface="MV Boli"/>
-        <a:font script="Deva" typeface="Mangal"/>
-        <a:font script="Telu" typeface="Gautami"/>
-        <a:font script="Taml" typeface="Latha"/>
-        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
-        <a:font script="Orya" typeface="Kalinga"/>
-        <a:font script="Mlym" typeface="Kartika"/>
-        <a:font script="Laoo" typeface="DokChampa"/>
-        <a:font script="Sinh" typeface="Iskoola Pota"/>
-        <a:font script="Mong" typeface="Mongolian Baiti"/>
-        <a:font script="Viet" typeface="Arial"/>
-        <a:font script="Uigh" typeface="Microsoft Uighur"/>
-      </a:minorFont>
-    </a:fontScheme>
-    <a:fmtScheme name="Office">
-      <a:fillStyleLst>
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:gradFill rotWithShape="1">
-          <a:gsLst>
-            <a:gs pos="0">
-              <a:schemeClr val="phClr">
-                <a:tint val="50000"/>
-                <a:satMod val="300000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="35000">
-              <a:schemeClr val="phClr">
-                <a:tint val="37000"/>
-                <a:satMod val="300000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="100000">
-              <a:schemeClr val="phClr">
-                <a:tint val="15000"/>
-                <a:satMod val="350000"/>
-              </a:schemeClr>
-            </a:gs>
-          </a:gsLst>
-          <a:lin ang="16200000" scaled="1"/>
-        </a:gradFill>
-        <a:gradFill rotWithShape="1">
-          <a:gsLst>
-            <a:gs pos="0">
-              <a:schemeClr val="phClr">
-                <a:shade val="51000"/>
-                <a:satMod val="130000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="80000">
-              <a:schemeClr val="phClr">
-                <a:shade val="93000"/>
-                <a:satMod val="130000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="100000">
-              <a:schemeClr val="phClr">
-                <a:shade val="94000"/>
-                <a:satMod val="135000"/>
-              </a:schemeClr>
-            </a:gs>
-          </a:gsLst>
-          <a:lin ang="16200000" scaled="0"/>
-        </a:gradFill>
-      </a:fillStyleLst>
-      <a:lnStyleLst>
-        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr">
-              <a:shade val="95000"/>
-              <a:satMod val="105000"/>
-            </a:schemeClr>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-        </a:ln>
-        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-        </a:ln>
-        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </a:lnStyleLst>
-      <a:effectStyleLst>
-        <a:effectStyle>
-          <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="20000" dir="5400000" rotWithShape="0">
-              <a:srgbClr val="000000">
-                <a:alpha val="38000"/>
-              </a:srgbClr>
-            </a:outerShdw>
-          </a:effectLst>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
-              <a:srgbClr val="000000">
-                <a:alpha val="35000"/>
-              </a:srgbClr>
-            </a:outerShdw>
-          </a:effectLst>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
-              <a:srgbClr val="000000">
-                <a:alpha val="35000"/>
-              </a:srgbClr>
-            </a:outerShdw>
-          </a:effectLst>
-          <a:scene3d>
-            <a:camera prst="orthographicFront">
-              <a:rot lat="0" lon="0" rev="0"/>
-            </a:camera>
-            <a:lightRig rig="threePt" dir="t">
-              <a:rot lat="0" lon="0" rev="1200000"/>
-            </a:lightRig>
-          </a:scene3d>
-          <a:sp3d>
-            <a:bevelT w="63500" h="25400"/>
-          </a:sp3d>
-        </a:effectStyle>
-      </a:effectStyleLst>
-      <a:bgFillStyleLst>
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:gradFill rotWithShape="1">
-          <a:gsLst>
-            <a:gs pos="0">
-              <a:schemeClr val="phClr">
-                <a:tint val="40000"/>
-                <a:satMod val="350000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="40000">
-              <a:schemeClr val="phClr">
-                <a:tint val="45000"/>
-                <a:shade val="99000"/>
-                <a:satMod val="350000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="100000">
-              <a:schemeClr val="phClr">
-                <a:shade val="20000"/>
-                <a:satMod val="255000"/>
-              </a:schemeClr>
-            </a:gs>
-          </a:gsLst>
-          <a:path path="circle">
-            <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
-          </a:path>
-        </a:gradFill>
-        <a:gradFill rotWithShape="1">
-          <a:gsLst>
-            <a:gs pos="0">
-              <a:schemeClr val="phClr">
-                <a:tint val="80000"/>
-                <a:satMod val="300000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="100000">
-              <a:schemeClr val="phClr">
-                <a:shade val="30000"/>
-                <a:satMod val="200000"/>
-              </a:schemeClr>
-            </a:gs>
-          </a:gsLst>
-          <a:path path="circle">
-            <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
-          </a:path>
-        </a:gradFill>
-      </a:bgFillStyleLst>
-    </a:fmtScheme>
-  </a:themeElements>
-  <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
-</a:theme>
-</file>
-
-<file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:p="http://schemas.openxmlformats.org/presentationml/2006/main" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -988,263 +707,279 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
-  <sheetFormatPr defaultColWidth="11.296875" defaultRowHeight="16.5"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:AR14"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.33203125" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col customWidth="1" min="1" max="1" width="27.19921875"/>
-    <col customWidth="1" min="2" max="2" width="30.59765625"/>
-    <col customWidth="1" min="3" max="3" width="40.3984375"/>
-    <col customWidth="1" min="4" max="4" width="42.09765625"/>
-    <col customWidth="1" min="5" max="8" width="15.296875"/>
-    <col customWidth="1" min="9" max="13" width="11.59765625"/>
-    <col customWidth="1" min="14" max="16" width="15.59765625"/>
-    <col customWidth="1" min="17" max="17" width="13.59765625"/>
-    <col customWidth="1" min="18" max="24" width="15.59765625"/>
-    <col customWidth="1" min="25" max="27" width="20.59765625"/>
-    <col customWidth="1" min="28" max="29" style="1" width="20.59765625"/>
-    <col customWidth="1" min="30" max="30" width="33.296875"/>
-    <col bestFit="1" customWidth="1" min="31" max="31" width="32.8984375"/>
-    <col bestFit="1" customWidth="1" min="32" max="32" width="31.09765625"/>
-    <col customWidth="1" min="33" max="33" width="20.59765625"/>
-    <col bestFit="1" min="34" max="34" width="21.125"/>
-    <col bestFit="1" min="35" max="35" width="18.75390625"/>
-    <col bestFit="1" min="36" max="36" width="10.125"/>
-    <col bestFit="1" min="37" max="37" width="16.50390625"/>
-    <col bestFit="1" min="38" max="38" width="16.875"/>
-    <col bestFit="1" min="39" max="39" width="13.00390625"/>
-    <col bestFit="1" min="40" max="40" width="22.00390625"/>
-    <col bestFit="1" min="41" max="41" width="24.375"/>
-    <col bestFit="1" min="42" max="42" width="14.375"/>
-    <col bestFit="1" min="43" max="44" width="29.125"/>
+    <col min="1" max="1" width="27.1640625" customWidth="1"/>
+    <col min="2" max="2" width="30.6640625" customWidth="1"/>
+    <col min="3" max="3" width="35.33203125" customWidth="1"/>
+    <col min="4" max="4" width="33.5" customWidth="1"/>
+    <col min="5" max="5" width="28.5" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="17.5" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="15.33203125" customWidth="1"/>
+    <col min="8" max="8" width="17.83203125" customWidth="1"/>
+    <col min="9" max="10" width="11.6640625" customWidth="1"/>
+    <col min="11" max="11" width="12.5" customWidth="1"/>
+    <col min="12" max="12" width="11" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="12.6640625" customWidth="1"/>
+    <col min="14" max="14" width="13.5" customWidth="1"/>
+    <col min="15" max="15" width="10.83203125" customWidth="1"/>
+    <col min="16" max="16" width="11.33203125" customWidth="1"/>
+    <col min="17" max="17" width="12.83203125" bestFit="1" customWidth="1"/>
+    <col min="18" max="23" width="9.5" customWidth="1"/>
+    <col min="24" max="24" width="16" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="18.83203125" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="20.6640625" customWidth="1"/>
+    <col min="28" max="28" width="20.6640625" style="1" customWidth="1"/>
+    <col min="29" max="29" width="20.1640625" style="1" customWidth="1"/>
+    <col min="30" max="30" width="33.33203125" customWidth="1"/>
+    <col min="31" max="32" width="25.6640625" customWidth="1"/>
+    <col min="33" max="33" width="17.5" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="21.1640625" customWidth="1"/>
+    <col min="35" max="35" width="20.6640625" customWidth="1"/>
+    <col min="36" max="36" width="20.33203125" customWidth="1"/>
+    <col min="37" max="37" width="16.83203125" customWidth="1"/>
+    <col min="38" max="38" width="16.6640625" customWidth="1"/>
+    <col min="39" max="39" width="18.1640625" customWidth="1"/>
+    <col min="40" max="40" width="22" customWidth="1"/>
+    <col min="41" max="41" width="24.33203125" customWidth="1"/>
+    <col min="42" max="42" width="16.33203125" bestFit="1" customWidth="1"/>
+    <col min="43" max="44" width="29.1640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="21">
+    <row r="1" spans="1:44" ht="21" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
       <c r="C1" s="2"/>
       <c r="D1" s="2"/>
       <c r="E1" s="2"/>
-      <c r="F1" s="3"/>
-      <c r="G1" s="3"/>
-      <c r="H1" s="3"/>
+      <c r="F1" s="2"/>
+      <c r="G1" s="2"/>
+      <c r="H1" s="2"/>
     </row>
-    <row r="2">
+    <row r="2" spans="1:44" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="4" t="s">
+      <c r="C2" s="3" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" spans="1:44" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>3</v>
       </c>
-      <c r="C3" s="5" t="s">
+      <c r="C3" s="14" t="s">
         <v>4</v>
       </c>
-      <c r="D3" s="5"/>
+      <c r="D3" s="14"/>
+      <c r="E3" s="14"/>
+      <c r="F3" s="15"/>
+      <c r="G3" s="15"/>
+      <c r="H3" s="15"/>
     </row>
-    <row r="4">
+    <row r="4" spans="1:44" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="6" t="s">
+    <row r="5" spans="1:44" ht="17" x14ac:dyDescent="0.2">
+      <c r="A5" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="C5" s="4" t="s">
+      <c r="C5" s="3" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="6" ht="47.399999999999999" customHeight="1">
-      <c r="C6" s="7" t="s">
+    <row r="6" spans="1:44" ht="47.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C6" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="D6" s="8" t="s">
+      <c r="D6" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="E6" s="8"/>
-      <c r="F6" s="8"/>
-      <c r="G6" s="8"/>
-      <c r="H6" s="8"/>
-      <c r="I6" s="8"/>
-      <c r="J6" s="8"/>
+      <c r="E6" s="13"/>
+      <c r="F6" s="13"/>
+      <c r="G6" s="13"/>
+      <c r="H6" s="13"/>
+      <c r="I6" s="13"/>
+      <c r="J6" s="13"/>
     </row>
-    <row r="7">
-      <c r="A7" s="9"/>
+    <row r="7" spans="1:44" x14ac:dyDescent="0.2">
+      <c r="A7" s="6"/>
     </row>
-    <row r="8">
-      <c r="A8" s="10"/>
+    <row r="8" spans="1:44" x14ac:dyDescent="0.2">
+      <c r="A8" s="7"/>
     </row>
-    <row r="9">
+    <row r="9" spans="1:44" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="10" s="11" customFormat="1" ht="49.5">
-      <c r="A10" s="12" t="s">
+    <row r="10" spans="1:44" s="8" customFormat="1" ht="52" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="B10" s="12" t="s">
+      <c r="B10" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="C10" s="12" t="s">
+      <c r="C10" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="D10" s="12" t="s">
+      <c r="D10" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="E10" s="12" t="s">
+      <c r="E10" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="F10" s="12" t="s">
+      <c r="F10" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="G10" s="12" t="s">
+      <c r="G10" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="H10" s="12" t="s">
+      <c r="H10" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="I10" s="12" t="s">
+      <c r="I10" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="J10" s="12" t="s">
+      <c r="J10" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="K10" s="12" t="s">
+      <c r="K10" s="10" t="s">
         <v>21</v>
       </c>
-      <c r="L10" s="12" t="s">
+      <c r="L10" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="M10" s="12" t="s">
+      <c r="M10" s="10" t="s">
         <v>23</v>
       </c>
-      <c r="N10" s="12" t="s">
+      <c r="N10" s="10" t="s">
         <v>23</v>
       </c>
-      <c r="O10" s="13" t="s">
+      <c r="O10" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="P10" s="13" t="s">
+      <c r="P10" s="16" t="s">
         <v>25</v>
       </c>
-      <c r="Q10" s="12" t="s">
+      <c r="Q10" s="10" t="s">
         <v>26</v>
       </c>
-      <c r="R10" s="12" t="s">
+      <c r="R10" s="9" t="s">
         <v>27</v>
       </c>
-      <c r="S10" s="12" t="s">
+      <c r="S10" s="9" t="s">
         <v>28</v>
       </c>
-      <c r="T10" s="12" t="s">
+      <c r="T10" s="9" t="s">
         <v>29</v>
       </c>
-      <c r="U10" s="12" t="s">
+      <c r="U10" s="9" t="s">
         <v>30</v>
       </c>
-      <c r="V10" s="12" t="s">
+      <c r="V10" s="9" t="s">
         <v>31</v>
       </c>
-      <c r="W10" s="12" t="s">
+      <c r="W10" s="9" t="s">
         <v>32</v>
       </c>
-      <c r="X10" s="13" t="s">
+      <c r="X10" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="Y10" s="13" t="s">
+      <c r="Y10" s="10" t="s">
         <v>8</v>
       </c>
-      <c r="Z10" s="12" t="s">
+      <c r="Z10" s="9" t="s">
         <v>34</v>
       </c>
-      <c r="AA10" s="14" t="s">
+      <c r="AA10" s="9" t="s">
         <v>34</v>
       </c>
-      <c r="AB10" s="15" t="s">
+      <c r="AB10" s="11" t="s">
         <v>35</v>
       </c>
-      <c r="AC10" s="15" t="s">
+      <c r="AC10" s="11" t="s">
         <v>36</v>
       </c>
-      <c r="AD10" s="12" t="s">
+      <c r="AD10" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="AE10" s="12" t="s">
+      <c r="AE10" s="9" t="s">
         <v>38</v>
       </c>
-      <c r="AF10" s="12" t="s">
+      <c r="AF10" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="AG10" s="12" t="s">
+      <c r="AG10" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="AH10" s="16" t="s">
+      <c r="AH10" s="9" t="s">
         <v>41</v>
       </c>
-      <c r="AI10" s="16" t="s">
+      <c r="AI10" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="AJ10" s="16" t="s">
+      <c r="AJ10" s="9" t="s">
         <v>43</v>
       </c>
-      <c r="AK10" s="16" t="s">
+      <c r="AK10" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="AL10" s="16" t="s">
+      <c r="AL10" s="9" t="s">
         <v>45</v>
       </c>
-      <c r="AM10" s="16" t="s">
+      <c r="AM10" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="AN10" s="16" t="s">
+      <c r="AN10" s="9" t="s">
         <v>47</v>
       </c>
-      <c r="AO10" s="16" t="s">
+      <c r="AO10" s="9" t="s">
         <v>48</v>
       </c>
-      <c r="AP10" s="16" t="s">
+      <c r="AP10" s="9" t="s">
         <v>49</v>
       </c>
-      <c r="AQ10" s="16" t="s">
+      <c r="AQ10" s="9" t="s">
         <v>50</v>
       </c>
-      <c r="AR10" s="17" t="s">
+      <c r="AR10" s="9" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="18" t="s">
+    <row r="11" spans="1:44" x14ac:dyDescent="0.2">
+      <c r="A11" s="17" t="s">
         <v>52</v>
       </c>
-      <c r="B11" s="18" t="s">
+      <c r="B11" s="17" t="s">
         <v>53</v>
       </c>
-      <c r="C11" s="18" t="s">
+      <c r="C11" s="17" t="s">
         <v>54</v>
       </c>
-      <c r="D11" s="18" t="s">
+      <c r="D11" s="17" t="s">
         <v>55</v>
       </c>
-      <c r="E11" s="18" t="s">
+      <c r="E11" s="17" t="s">
         <v>56</v>
       </c>
-      <c r="F11" s="19" t="s">
+      <c r="F11" s="17" t="s">
         <v>57</v>
       </c>
-      <c r="G11" s="19" t="s">
+      <c r="G11" s="17" t="s">
         <v>58</v>
       </c>
-      <c r="H11" s="19" t="s">
+      <c r="H11" s="17" t="s">
         <v>59</v>
       </c>
       <c r="I11" s="18" t="s">
@@ -1256,13 +991,13 @@
       <c r="K11" s="18" t="s">
         <v>62</v>
       </c>
-      <c r="L11" s="20" t="s">
+      <c r="L11" s="18" t="s">
         <v>63</v>
       </c>
-      <c r="M11" s="20" t="s">
+      <c r="M11" s="18" t="s">
         <v>64</v>
       </c>
-      <c r="N11" s="20" t="s">
+      <c r="N11" s="18" t="s">
         <v>65</v>
       </c>
       <c r="O11" s="18" t="s">
@@ -1274,22 +1009,22 @@
       <c r="Q11" s="18" t="s">
         <v>68</v>
       </c>
-      <c r="R11" s="20" t="s">
+      <c r="R11" s="18" t="s">
         <v>69</v>
       </c>
-      <c r="S11" s="20" t="s">
+      <c r="S11" s="18" t="s">
         <v>70</v>
       </c>
-      <c r="T11" s="20" t="s">
+      <c r="T11" s="18" t="s">
         <v>71</v>
       </c>
-      <c r="U11" s="20" t="s">
+      <c r="U11" s="18" t="s">
         <v>72</v>
       </c>
-      <c r="V11" s="20" t="s">
+      <c r="V11" s="18" t="s">
         <v>73</v>
       </c>
-      <c r="W11" s="20" t="s">
+      <c r="W11" s="18" t="s">
         <v>74</v>
       </c>
       <c r="X11" s="18" t="s">
@@ -1298,10 +1033,10 @@
       <c r="Y11" s="18" t="s">
         <v>76</v>
       </c>
-      <c r="Z11" s="18" t="s">
+      <c r="Z11" s="19" t="s">
         <v>77</v>
       </c>
-      <c r="AA11" s="18" t="s">
+      <c r="AA11" s="20" t="s">
         <v>78</v>
       </c>
       <c r="AB11" s="21" t="e">
@@ -1316,10 +1051,10 @@
         <f>IF(AC11&gt;0.05,"Високий рівень помилок/недійсних даних. Звертайтесь до лаб.","")</f>
         <v>#VALUE!</v>
       </c>
-      <c r="AE11" s="22" t="s">
+      <c r="AE11" s="19" t="s">
         <v>79</v>
       </c>
-      <c r="AF11" s="22" t="s">
+      <c r="AF11" s="19" t="s">
         <v>80</v>
       </c>
       <c r="AG11" s="18" t="s">
@@ -1349,7 +1084,7 @@
       <c r="AO11" s="23" t="s">
         <v>89</v>
       </c>
-      <c r="AP11" s="24" t="s">
+      <c r="AP11" s="25" t="s">
         <v>90</v>
       </c>
       <c r="AQ11" s="24" t="s">
@@ -1359,23 +1094,21 @@
         <v>92</v>
       </c>
     </row>
-    <row r="14">
-      <c r="B14" s="25"/>
-      <c r="C14" s="25"/>
-      <c r="D14" s="25"/>
-      <c r="E14" s="25"/>
-      <c r="F14" s="26"/>
-      <c r="G14" s="26"/>
-      <c r="H14" s="26"/>
+    <row r="14" spans="1:44" x14ac:dyDescent="0.2">
+      <c r="B14" s="12"/>
+      <c r="C14" s="12"/>
+      <c r="D14" s="12"/>
+      <c r="E14" s="12"/>
+      <c r="F14" s="12"/>
+      <c r="G14" s="12"/>
+      <c r="H14" s="12"/>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="C3:D3"/>
     <mergeCell ref="D6:J6"/>
+    <mergeCell ref="C3:E3"/>
   </mergeCells>
-  <printOptions headings="0" gridLines="0"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.51181102362204689" footer="0.51181102362204689"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" cellComments="none" useFirstPageNumber="0" errors="displayed" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
 </file>
--- a/api/templates/genxpert_tb_workload_report/uk.xlsx
+++ b/api/templates/genxpert_tb_workload_report/uk.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10309"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10531"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ahernandez/repos/aspect/api/templates/genxpert_tb_workload_report/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{32563A87-7BA4-364A-8E12-9B5AD0E0FCFB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E34DF97E-650E-7548-89DD-E65C45134AF1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="760" windowWidth="34560" windowHeight="21580" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -453,12 +453,6 @@
     </xf>
     <xf numFmtId="10" fontId="6" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
@@ -477,6 +471,12 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="10" fontId="7" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="14" fontId="1" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -717,7 +717,7 @@
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.33203125" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="27.1640625" customWidth="1"/>
-    <col min="2" max="2" width="30.6640625" customWidth="1"/>
+    <col min="2" max="2" width="10.83203125" customWidth="1"/>
     <col min="3" max="3" width="35.33203125" customWidth="1"/>
     <col min="4" max="4" width="33.5" customWidth="1"/>
     <col min="5" max="5" width="28.5" bestFit="1" customWidth="1"/>
@@ -772,18 +772,18 @@
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="1:44" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:44" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>3</v>
       </c>
-      <c r="C3" s="14" t="s">
+      <c r="C3" s="22" t="s">
         <v>4</v>
       </c>
-      <c r="D3" s="14"/>
-      <c r="E3" s="14"/>
-      <c r="F3" s="15"/>
-      <c r="G3" s="15"/>
-      <c r="H3" s="15"/>
+      <c r="D3" s="22"/>
+      <c r="E3" s="22"/>
+      <c r="F3" s="13"/>
+      <c r="G3" s="13"/>
+      <c r="H3" s="13"/>
     </row>
     <row r="4" spans="1:44" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
@@ -802,15 +802,15 @@
       <c r="C6" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="D6" s="13" t="s">
+      <c r="D6" s="21" t="s">
         <v>9</v>
       </c>
-      <c r="E6" s="13"/>
-      <c r="F6" s="13"/>
-      <c r="G6" s="13"/>
-      <c r="H6" s="13"/>
-      <c r="I6" s="13"/>
-      <c r="J6" s="13"/>
+      <c r="E6" s="21"/>
+      <c r="F6" s="21"/>
+      <c r="G6" s="21"/>
+      <c r="H6" s="21"/>
+      <c r="I6" s="21"/>
+      <c r="J6" s="21"/>
     </row>
     <row r="7" spans="1:44" x14ac:dyDescent="0.2">
       <c r="A7" s="6"/>
@@ -825,10 +825,10 @@
     </row>
     <row r="10" spans="1:44" s="8" customFormat="1" ht="52" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A10" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="B10" s="9" t="s">
         <v>11</v>
-      </c>
-      <c r="B10" s="9" t="s">
-        <v>12</v>
       </c>
       <c r="C10" s="9" t="s">
         <v>13</v>
@@ -869,7 +869,7 @@
       <c r="O10" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="P10" s="16" t="s">
+      <c r="P10" s="14" t="s">
         <v>25</v>
       </c>
       <c r="Q10" s="10" t="s">
@@ -958,106 +958,106 @@
       </c>
     </row>
     <row r="11" spans="1:44" x14ac:dyDescent="0.2">
-      <c r="A11" s="17" t="s">
+      <c r="A11" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="B11" s="15" t="s">
         <v>52</v>
       </c>
-      <c r="B11" s="17" t="s">
-        <v>53</v>
-      </c>
-      <c r="C11" s="17" t="s">
+      <c r="C11" s="15" t="s">
         <v>54</v>
       </c>
-      <c r="D11" s="17" t="s">
+      <c r="D11" s="15" t="s">
         <v>55</v>
       </c>
-      <c r="E11" s="17" t="s">
+      <c r="E11" s="15" t="s">
         <v>56</v>
       </c>
-      <c r="F11" s="17" t="s">
+      <c r="F11" s="15" t="s">
         <v>57</v>
       </c>
-      <c r="G11" s="17" t="s">
+      <c r="G11" s="15" t="s">
         <v>58</v>
       </c>
-      <c r="H11" s="17" t="s">
+      <c r="H11" s="15" t="s">
         <v>59</v>
       </c>
-      <c r="I11" s="18" t="s">
+      <c r="I11" s="16" t="s">
         <v>60</v>
       </c>
-      <c r="J11" s="18" t="s">
+      <c r="J11" s="16" t="s">
         <v>61</v>
       </c>
-      <c r="K11" s="18" t="s">
+      <c r="K11" s="16" t="s">
         <v>62</v>
       </c>
-      <c r="L11" s="18" t="s">
+      <c r="L11" s="16" t="s">
         <v>63</v>
       </c>
-      <c r="M11" s="18" t="s">
+      <c r="M11" s="16" t="s">
         <v>64</v>
       </c>
-      <c r="N11" s="18" t="s">
+      <c r="N11" s="16" t="s">
         <v>65</v>
       </c>
-      <c r="O11" s="18" t="s">
+      <c r="O11" s="16" t="s">
         <v>66</v>
       </c>
-      <c r="P11" s="18" t="s">
+      <c r="P11" s="16" t="s">
         <v>67</v>
       </c>
-      <c r="Q11" s="18" t="s">
+      <c r="Q11" s="16" t="s">
         <v>68</v>
       </c>
-      <c r="R11" s="18" t="s">
+      <c r="R11" s="16" t="s">
         <v>69</v>
       </c>
-      <c r="S11" s="18" t="s">
+      <c r="S11" s="16" t="s">
         <v>70</v>
       </c>
-      <c r="T11" s="18" t="s">
+      <c r="T11" s="16" t="s">
         <v>71</v>
       </c>
-      <c r="U11" s="18" t="s">
+      <c r="U11" s="16" t="s">
         <v>72</v>
       </c>
-      <c r="V11" s="18" t="s">
+      <c r="V11" s="16" t="s">
         <v>73</v>
       </c>
-      <c r="W11" s="18" t="s">
+      <c r="W11" s="16" t="s">
         <v>74</v>
       </c>
-      <c r="X11" s="18" t="s">
+      <c r="X11" s="16" t="s">
         <v>75</v>
       </c>
-      <c r="Y11" s="18" t="s">
+      <c r="Y11" s="16" t="s">
         <v>76</v>
       </c>
-      <c r="Z11" s="19" t="s">
+      <c r="Z11" s="17" t="s">
         <v>77</v>
       </c>
-      <c r="AA11" s="20" t="s">
+      <c r="AA11" s="18" t="s">
         <v>78</v>
       </c>
-      <c r="AB11" s="21" t="e">
+      <c r="AB11" s="19" t="e">
         <f>IF(AG11=0,0,L11/AG11)</f>
         <v>#VALUE!</v>
       </c>
-      <c r="AC11" s="22" t="e">
+      <c r="AC11" s="20" t="e">
         <f>IF(AG11=0,0,(L11+M11)/AG11)</f>
         <v>#VALUE!</v>
       </c>
-      <c r="AD11" s="22" t="e">
+      <c r="AD11" s="20" t="e">
         <f>IF(AC11&gt;0.05,"Високий рівень помилок/недійсних даних. Звертайтесь до лаб.","")</f>
         <v>#VALUE!</v>
       </c>
-      <c r="AE11" s="19" t="s">
+      <c r="AE11" s="17" t="s">
         <v>79</v>
       </c>
-      <c r="AF11" s="19" t="s">
+      <c r="AF11" s="17" t="s">
         <v>80</v>
       </c>
-      <c r="AG11" s="18" t="s">
+      <c r="AG11" s="16" t="s">
         <v>81</v>
       </c>
       <c r="AH11" s="23" t="s">

--- a/api/templates/genxpert_tb_workload_report/uk.xlsx
+++ b/api/templates/genxpert_tb_workload_report/uk.xlsx
@@ -1,39 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10531"/>
-  <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ahernandez/repos/aspect/api/templates/genxpert_tb_workload_report/"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E34DF97E-650E-7548-89DD-E65C45134AF1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
+  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="760" windowWidth="34560" windowHeight="21580" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="760" windowWidth="34560" windowHeight="21580"/>
   </bookViews>
   <sheets>
-    <sheet name="Пристрої" sheetId="1" r:id="rId1"/>
+    <sheet sheetId="1" name="Пристрої" state="visible" r:id="rId4"/>
   </sheets>
-  <calcPr calcId="191029" iterateDelta="1E-4"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="93">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="90">
   <si>
     <t>Пристрої GeneXpert</t>
   </si>
@@ -62,18 +43,15 @@
     <t># Використовувані модулі</t>
   </si>
   <si>
-    <t>Підраховує кількість днів, коли пристрій принаймні один раз повідомлялося про будь-який із статусів неактивності (включно зі статусами «Невідомо» та «Тестування не проводилися»).</t>
-  </si>
-  <si>
     <t>&lt;Table&gt;</t>
   </si>
   <si>
+    <t>Назва сайту</t>
+  </si>
+  <si>
     <t>пристрій</t>
   </si>
   <si>
-    <t>Назва сайту</t>
-  </si>
-  <si>
     <t>Держава</t>
   </si>
   <si>
@@ -83,9 +61,6 @@
     <t>Серійний</t>
   </si>
   <si>
-    <t>Серійний номер інструменту</t>
-  </si>
-  <si>
     <t>Cтатус</t>
   </si>
   <si>
@@ -191,12 +166,12 @@
     <t>Реєстраційний номер SIM-карти №2</t>
   </si>
   <si>
+    <t>&lt;siteName&gt;</t>
+  </si>
+  <si>
     <t>&lt;name&gt;</t>
   </si>
   <si>
-    <t>&lt;siteName&gt;</t>
-  </si>
-  <si>
     <t>&lt;stateName&gt;</t>
   </si>
   <si>
@@ -204,9 +179,6 @@
   </si>
   <si>
     <t>&lt;serial&gt;</t>
-  </si>
-  <si>
-    <t>&lt;lastInstrumentSerial&gt;</t>
   </si>
   <si>
     <t>&lt;maintenanceStatusName&gt;</t>
@@ -317,62 +289,69 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd\ hh:mm"/>
+    <numFmt numFmtId="164" formatCode="yyyy-mm-dd hh:mm"/>
   </numFmts>
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
-      <sz val="12"/>
-      <color indexed="64"/>
+      <color theme="1"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+      <sz val="11"/>
       <name val="Calibri"/>
     </font>
     <font>
+      <color indexed="64"/>
       <sz val="12"/>
-      <color theme="1"/>
       <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <b/>
+      <color indexed="64"/>
+      <family val="2"/>
       <sz val="16"/>
-      <color indexed="64"/>
       <name val="Calibri"/>
-      <family val="2"/>
     </font>
     <font>
       <u/>
+      <color indexed="64"/>
+      <family val="2"/>
       <sz val="12"/>
-      <color indexed="64"/>
       <name val="Calibri"/>
-      <family val="2"/>
     </font>
     <font>
       <i/>
+      <color indexed="64"/>
+      <family val="2"/>
       <sz val="12"/>
-      <color indexed="64"/>
       <name val="Calibri"/>
-      <family val="2"/>
     </font>
     <font>
       <b/>
+      <color indexed="64"/>
+      <family val="2"/>
       <sz val="12"/>
-      <color indexed="64"/>
       <name val="Calibri"/>
-      <family val="2"/>
     </font>
     <font>
       <b/>
+      <family val="2"/>
       <sz val="12"/>
       <name val="Calibri"/>
-      <family val="2"/>
     </font>
     <font>
+      <color indexed="64"/>
+      <family val="2"/>
       <sz val="12"/>
-      <color indexed="64"/>
       <name val="Calibri"/>
+    </font>
+    <font>
+      <color theme="1"/>
       <family val="2"/>
+      <scheme val="minor"/>
+      <sz val="12"/>
+      <name val="Calibri"/>
     </font>
   </fonts>
   <fills count="3">
@@ -398,47 +377,39 @@
       <diagonal/>
     </border>
     <border>
-      <left style="medium">
-        <color auto="1"/>
-      </left>
-      <right style="medium">
-        <color auto="1"/>
-      </right>
-      <top style="medium">
-        <color auto="1"/>
-      </top>
-      <bottom style="medium">
-        <color auto="1"/>
-      </bottom>
+      <left style="medium"/>
+      <right style="medium"/>
+      <top style="medium"/>
+      <bottom style="medium"/>
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
+      <left style="thin"/>
+      <right style="thin"/>
       <top/>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
+      <bottom style="thin"/>
       <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="10" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -451,14 +422,10 @@
     <xf numFmtId="164" fontId="6" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="10" fontId="6" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="10" fontId="6" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
@@ -471,21 +438,16 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="10" fontId="7" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="8" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="8" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -712,48 +674,47 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:AR14"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.33203125" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="16" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.2" defaultColWidth="11.33203125" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="27.1640625" customWidth="1"/>
     <col min="2" max="2" width="10.83203125" customWidth="1"/>
     <col min="3" max="3" width="35.33203125" customWidth="1"/>
     <col min="4" max="4" width="33.5" customWidth="1"/>
-    <col min="5" max="5" width="28.5" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="17.5" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="15.33203125" customWidth="1"/>
-    <col min="8" max="8" width="17.83203125" customWidth="1"/>
-    <col min="9" max="10" width="11.6640625" customWidth="1"/>
-    <col min="11" max="11" width="12.5" customWidth="1"/>
-    <col min="12" max="12" width="11" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="12.6640625" customWidth="1"/>
-    <col min="14" max="14" width="13.5" customWidth="1"/>
-    <col min="15" max="15" width="10.83203125" customWidth="1"/>
-    <col min="16" max="16" width="11.33203125" customWidth="1"/>
-    <col min="17" max="17" width="12.83203125" bestFit="1" customWidth="1"/>
-    <col min="18" max="23" width="9.5" customWidth="1"/>
-    <col min="24" max="24" width="16" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="18.83203125" bestFit="1" customWidth="1"/>
-    <col min="26" max="27" width="20.6640625" customWidth="1"/>
-    <col min="28" max="28" width="20.6640625" style="1" customWidth="1"/>
-    <col min="29" max="29" width="20.1640625" style="1" customWidth="1"/>
-    <col min="30" max="30" width="33.33203125" customWidth="1"/>
-    <col min="31" max="32" width="25.6640625" customWidth="1"/>
-    <col min="33" max="33" width="17.5" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="21.1640625" customWidth="1"/>
-    <col min="35" max="35" width="20.6640625" customWidth="1"/>
-    <col min="36" max="36" width="20.33203125" customWidth="1"/>
-    <col min="37" max="37" width="16.83203125" customWidth="1"/>
-    <col min="38" max="38" width="16.6640625" customWidth="1"/>
-    <col min="39" max="39" width="18.1640625" customWidth="1"/>
-    <col min="40" max="40" width="22" customWidth="1"/>
-    <col min="41" max="41" width="24.33203125" customWidth="1"/>
-    <col min="42" max="42" width="16.33203125" bestFit="1" customWidth="1"/>
-    <col min="43" max="44" width="29.1640625" customWidth="1"/>
+    <col min="5" max="5" width="28.5" customWidth="1"/>
+    <col min="6" max="6" width="15.33203125" customWidth="1"/>
+    <col min="7" max="7" width="17.83203125" customWidth="1"/>
+    <col min="8" max="9" width="11.6640625" customWidth="1"/>
+    <col min="10" max="10" width="12.5" customWidth="1"/>
+    <col min="11" max="11" width="11" customWidth="1"/>
+    <col min="12" max="12" width="12.6640625" customWidth="1"/>
+    <col min="13" max="13" width="13.5" customWidth="1"/>
+    <col min="14" max="14" width="10.83203125" customWidth="1"/>
+    <col min="15" max="15" width="11.33203125" customWidth="1"/>
+    <col min="16" max="16" width="12.83203125" customWidth="1"/>
+    <col min="17" max="22" width="9.5" customWidth="1"/>
+    <col min="23" max="23" width="16" customWidth="1"/>
+    <col min="24" max="24" width="18.83203125" customWidth="1"/>
+    <col min="25" max="26" width="20.6640625" customWidth="1"/>
+    <col min="27" max="27" width="20.6640625" style="1" customWidth="1"/>
+    <col min="28" max="28" width="20.1640625" style="1" customWidth="1"/>
+    <col min="29" max="29" width="33.33203125" customWidth="1"/>
+    <col min="30" max="31" width="25.6640625" customWidth="1"/>
+    <col min="32" max="32" width="17.5" customWidth="1"/>
+    <col min="33" max="33" width="21.1640625" customWidth="1"/>
+    <col min="34" max="34" width="20.6640625" customWidth="1"/>
+    <col min="35" max="35" width="20.33203125" customWidth="1"/>
+    <col min="36" max="36" width="16.83203125" customWidth="1"/>
+    <col min="37" max="37" width="16.6640625" customWidth="1"/>
+    <col min="38" max="38" width="18.1640625" customWidth="1"/>
+    <col min="39" max="39" width="22" customWidth="1"/>
+    <col min="40" max="40" width="24.33203125" customWidth="1"/>
+    <col min="41" max="41" width="16.33203125" customWidth="1"/>
+    <col min="42" max="43" width="29.1640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:44" ht="21" x14ac:dyDescent="0.25">
+    <row r="1" ht="21" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -762,9 +723,8 @@
       <c r="E1" s="2"/>
       <c r="F1" s="2"/>
       <c r="G1" s="2"/>
-      <c r="H1" s="2"/>
-    </row>
-    <row r="2" spans="1:44" x14ac:dyDescent="0.2">
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -772,343 +732,333 @@
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="1:44" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" ht="16" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>3</v>
       </c>
-      <c r="C3" s="22" t="s">
+      <c r="C3" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="D3" s="22"/>
-      <c r="E3" s="22"/>
-      <c r="F3" s="13"/>
-      <c r="G3" s="13"/>
-      <c r="H3" s="13"/>
-    </row>
-    <row r="4" spans="1:44" x14ac:dyDescent="0.2">
+      <c r="D3" s="4"/>
+      <c r="E3" s="4"/>
+      <c r="F3" s="4"/>
+      <c r="G3" s="4"/>
+    </row>
+    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="5" spans="1:44" ht="17" x14ac:dyDescent="0.2">
-      <c r="A5" s="4" t="s">
+    <row r="5" ht="17" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C5" s="3" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="6" spans="1:44" ht="47.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C6" s="5" t="s">
+    <row r="6" ht="47.5" customHeight="1" spans="3:10" x14ac:dyDescent="0.25">
+      <c r="C6" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="D6" s="21" t="s">
+      <c r="D6" s="7"/>
+      <c r="E6" s="7"/>
+      <c r="F6" s="7"/>
+      <c r="G6" s="7"/>
+      <c r="H6" s="7"/>
+      <c r="I6" s="7"/>
+      <c r="J6"/>
+    </row>
+    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A7" s="8"/>
+    </row>
+    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A8" s="9"/>
+    </row>
+    <row r="9" ht="17" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
         <v>9</v>
       </c>
-      <c r="E6" s="21"/>
-      <c r="F6" s="21"/>
-      <c r="G6" s="21"/>
-      <c r="H6" s="21"/>
-      <c r="I6" s="21"/>
-      <c r="J6" s="21"/>
-    </row>
-    <row r="7" spans="1:44" x14ac:dyDescent="0.2">
-      <c r="A7" s="6"/>
-    </row>
-    <row r="8" spans="1:44" x14ac:dyDescent="0.2">
-      <c r="A8" s="7"/>
-    </row>
-    <row r="9" spans="1:44" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
+    </row>
+    <row r="10" ht="52" customHeight="1" spans="1:44" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="11" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="10" spans="1:44" s="8" customFormat="1" ht="52" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="9" t="s">
+      <c r="B10" s="11" t="s">
+        <v>11</v>
+      </c>
+      <c r="C10" s="11" t="s">
         <v>12</v>
       </c>
-      <c r="B10" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="C10" s="9" t="s">
+      <c r="D10" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="D10" s="9" t="s">
+      <c r="E10" s="11" t="s">
         <v>14</v>
       </c>
-      <c r="E10" s="9" t="s">
+      <c r="F10" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="F10" s="9" t="s">
+      <c r="G10" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="G10" s="9" t="s">
+      <c r="H10" s="11" t="s">
         <v>17</v>
       </c>
-      <c r="H10" s="9" t="s">
+      <c r="I10" s="11" t="s">
         <v>18</v>
       </c>
-      <c r="I10" s="9" t="s">
+      <c r="J10" s="12" t="s">
         <v>19</v>
       </c>
-      <c r="J10" s="9" t="s">
+      <c r="K10" s="12" t="s">
         <v>20</v>
       </c>
-      <c r="K10" s="10" t="s">
+      <c r="L10" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="L10" s="10" t="s">
+      <c r="M10" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="N10" s="12" t="s">
         <v>22</v>
       </c>
-      <c r="M10" s="10" t="s">
+      <c r="O10" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="N10" s="10" t="s">
-        <v>23</v>
-      </c>
-      <c r="O10" s="10" t="s">
+      <c r="P10" s="12" t="s">
         <v>24</v>
       </c>
-      <c r="P10" s="14" t="s">
+      <c r="Q10" s="11" t="s">
         <v>25</v>
       </c>
-      <c r="Q10" s="10" t="s">
+      <c r="R10" s="11" t="s">
         <v>26</v>
       </c>
-      <c r="R10" s="9" t="s">
+      <c r="S10" s="11" t="s">
         <v>27</v>
       </c>
-      <c r="S10" s="9" t="s">
+      <c r="T10" s="11" t="s">
         <v>28</v>
       </c>
-      <c r="T10" s="9" t="s">
+      <c r="U10" s="11" t="s">
         <v>29</v>
       </c>
-      <c r="U10" s="9" t="s">
+      <c r="V10" s="11" t="s">
         <v>30</v>
       </c>
-      <c r="V10" s="9" t="s">
+      <c r="W10" s="12" t="s">
         <v>31</v>
       </c>
-      <c r="W10" s="9" t="s">
+      <c r="X10" s="12" t="s">
+        <v>8</v>
+      </c>
+      <c r="Y10" s="11" t="s">
         <v>32</v>
       </c>
-      <c r="X10" s="10" t="s">
+      <c r="Z10" s="11" t="s">
+        <v>32</v>
+      </c>
+      <c r="AA10" s="14" t="s">
         <v>33</v>
       </c>
-      <c r="Y10" s="10" t="s">
-        <v>8</v>
-      </c>
-      <c r="Z10" s="9" t="s">
+      <c r="AB10" s="14" t="s">
         <v>34</v>
       </c>
-      <c r="AA10" s="9" t="s">
-        <v>34</v>
-      </c>
-      <c r="AB10" s="11" t="s">
+      <c r="AC10" s="11" t="s">
         <v>35</v>
       </c>
-      <c r="AC10" s="11" t="s">
+      <c r="AD10" s="11" t="s">
         <v>36</v>
       </c>
-      <c r="AD10" s="9" t="s">
+      <c r="AE10" s="11" t="s">
         <v>37</v>
       </c>
-      <c r="AE10" s="9" t="s">
+      <c r="AF10" s="11" t="s">
         <v>38</v>
       </c>
-      <c r="AF10" s="9" t="s">
+      <c r="AG10" s="11" t="s">
         <v>39</v>
       </c>
-      <c r="AG10" s="9" t="s">
+      <c r="AH10" s="11" t="s">
         <v>40</v>
       </c>
-      <c r="AH10" s="9" t="s">
+      <c r="AI10" s="11" t="s">
         <v>41</v>
       </c>
-      <c r="AI10" s="9" t="s">
+      <c r="AJ10" s="11" t="s">
         <v>42</v>
       </c>
-      <c r="AJ10" s="9" t="s">
+      <c r="AK10" s="11" t="s">
         <v>43</v>
       </c>
-      <c r="AK10" s="9" t="s">
+      <c r="AL10" s="11" t="s">
         <v>44</v>
       </c>
-      <c r="AL10" s="9" t="s">
+      <c r="AM10" s="11" t="s">
         <v>45</v>
       </c>
-      <c r="AM10" s="9" t="s">
+      <c r="AN10" s="11" t="s">
         <v>46</v>
       </c>
-      <c r="AN10" s="9" t="s">
+      <c r="AO10" s="11" t="s">
         <v>47</v>
       </c>
-      <c r="AO10" s="9" t="s">
+      <c r="AP10" s="11" t="s">
         <v>48</v>
       </c>
-      <c r="AP10" s="9" t="s">
+      <c r="AQ10" s="11" t="s">
         <v>49</v>
       </c>
-      <c r="AQ10" s="9" t="s">
+    </row>
+    <row r="11" spans="1:44" x14ac:dyDescent="0.25">
+      <c r="A11" s="15" t="s">
         <v>50</v>
       </c>
-      <c r="AR10" s="9" t="s">
+      <c r="B11" s="15" t="s">
         <v>51</v>
       </c>
-    </row>
-    <row r="11" spans="1:44" x14ac:dyDescent="0.2">
-      <c r="A11" s="15" t="s">
+      <c r="C11" s="15" t="s">
+        <v>52</v>
+      </c>
+      <c r="D11" s="15" t="s">
         <v>53</v>
       </c>
-      <c r="B11" s="15" t="s">
-        <v>52</v>
-      </c>
-      <c r="C11" s="15" t="s">
+      <c r="E11" s="15" t="s">
         <v>54</v>
       </c>
-      <c r="D11" s="15" t="s">
+      <c r="F11" s="15" t="s">
         <v>55</v>
       </c>
-      <c r="E11" s="15" t="s">
+      <c r="G11" s="15" t="s">
         <v>56</v>
       </c>
-      <c r="F11" s="15" t="s">
+      <c r="H11" s="16" t="s">
         <v>57</v>
       </c>
-      <c r="G11" s="15" t="s">
+      <c r="I11" s="16" t="s">
         <v>58</v>
       </c>
-      <c r="H11" s="15" t="s">
+      <c r="J11" s="16" t="s">
         <v>59</v>
       </c>
-      <c r="I11" s="16" t="s">
+      <c r="K11" s="16" t="s">
         <v>60</v>
       </c>
-      <c r="J11" s="16" t="s">
+      <c r="L11" s="16" t="s">
         <v>61</v>
       </c>
-      <c r="K11" s="16" t="s">
+      <c r="M11" s="16" t="s">
         <v>62</v>
       </c>
-      <c r="L11" s="16" t="s">
+      <c r="N11" s="16" t="s">
         <v>63</v>
       </c>
-      <c r="M11" s="16" t="s">
+      <c r="O11" s="16" t="s">
         <v>64</v>
       </c>
-      <c r="N11" s="16" t="s">
+      <c r="P11" s="16" t="s">
         <v>65</v>
       </c>
-      <c r="O11" s="16" t="s">
+      <c r="Q11" s="16" t="s">
         <v>66</v>
       </c>
-      <c r="P11" s="16" t="s">
+      <c r="R11" s="16" t="s">
         <v>67</v>
       </c>
-      <c r="Q11" s="16" t="s">
+      <c r="S11" s="16" t="s">
         <v>68</v>
       </c>
-      <c r="R11" s="16" t="s">
+      <c r="T11" s="16" t="s">
         <v>69</v>
       </c>
-      <c r="S11" s="16" t="s">
+      <c r="U11" s="16" t="s">
         <v>70</v>
       </c>
-      <c r="T11" s="16" t="s">
+      <c r="V11" s="16" t="s">
         <v>71</v>
       </c>
-      <c r="U11" s="16" t="s">
+      <c r="W11" s="16" t="s">
         <v>72</v>
       </c>
-      <c r="V11" s="16" t="s">
+      <c r="X11" s="16" t="s">
         <v>73</v>
       </c>
-      <c r="W11" s="16" t="s">
+      <c r="Y11" s="17" t="s">
         <v>74</v>
       </c>
-      <c r="X11" s="16" t="s">
+      <c r="Z11" s="18" t="s">
         <v>75</v>
       </c>
-      <c r="Y11" s="16" t="s">
-        <v>76</v>
-      </c>
-      <c r="Z11" s="17" t="s">
-        <v>77</v>
-      </c>
-      <c r="AA11" s="18" t="s">
-        <v>78</v>
-      </c>
-      <c r="AB11" s="19" t="e">
+      <c r="AA11" s="19" t="e">
         <f>IF(AG11=0,0,L11/AG11)</f>
         <v>#VALUE!</v>
       </c>
-      <c r="AC11" s="20" t="e">
+      <c r="AB11" s="20" t="e">
         <f>IF(AG11=0,0,(L11+M11)/AG11)</f>
         <v>#VALUE!</v>
       </c>
-      <c r="AD11" s="20" t="e">
+      <c r="AC11" s="20" t="e">
         <f>IF(AC11&gt;0.05,"Високий рівень помилок/недійсних даних. Звертайтесь до лаб.","")</f>
         <v>#VALUE!</v>
       </c>
+      <c r="AD11" s="17" t="s">
+        <v>76</v>
+      </c>
       <c r="AE11" s="17" t="s">
+        <v>77</v>
+      </c>
+      <c r="AF11" s="16" t="s">
+        <v>78</v>
+      </c>
+      <c r="AG11" s="21" t="s">
         <v>79</v>
       </c>
-      <c r="AF11" s="17" t="s">
+      <c r="AH11" s="22" t="s">
         <v>80</v>
       </c>
-      <c r="AG11" s="16" t="s">
+      <c r="AI11" s="22" t="s">
         <v>81</v>
       </c>
-      <c r="AH11" s="23" t="s">
+      <c r="AJ11" s="22" t="s">
         <v>82</v>
       </c>
-      <c r="AI11" s="24" t="s">
+      <c r="AK11" s="22" t="s">
         <v>83</v>
       </c>
-      <c r="AJ11" s="24" t="s">
+      <c r="AL11" s="22" t="s">
         <v>84</v>
       </c>
-      <c r="AK11" s="24" t="s">
+      <c r="AM11" s="22" t="s">
         <v>85</v>
       </c>
-      <c r="AL11" s="24" t="s">
+      <c r="AN11" s="21" t="s">
         <v>86</v>
       </c>
-      <c r="AM11" s="24" t="s">
+      <c r="AO11" s="23" t="s">
         <v>87</v>
       </c>
-      <c r="AN11" s="24" t="s">
+      <c r="AP11" s="22" t="s">
         <v>88</v>
       </c>
-      <c r="AO11" s="23" t="s">
+      <c r="AQ11" s="22" t="s">
         <v>89</v>
       </c>
-      <c r="AP11" s="25" t="s">
-        <v>90</v>
-      </c>
-      <c r="AQ11" s="24" t="s">
-        <v>91</v>
-      </c>
-      <c r="AR11" s="24" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="14" spans="1:44" x14ac:dyDescent="0.2">
-      <c r="B14" s="12"/>
-      <c r="C14" s="12"/>
-      <c r="D14" s="12"/>
-      <c r="E14" s="12"/>
-      <c r="F14" s="12"/>
-      <c r="G14" s="12"/>
-      <c r="H14" s="12"/>
+    </row>
+    <row r="14" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B14" s="24"/>
+      <c r="C14" s="24"/>
+      <c r="D14" s="24"/>
+      <c r="E14" s="24"/>
+      <c r="F14" s="24"/>
+      <c r="G14" s="24"/>
     </row>
   </sheetData>
   <mergeCells count="2">
+    <mergeCell ref="C3:E3"/>
     <mergeCell ref="D6:J6"/>
-    <mergeCell ref="C3:E3"/>
   </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.51181102362204689" footer="0.51181102362204689"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5118110236220469" footer="0.5118110236220469"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
 </file>
--- a/api/templates/genxpert_tb_workload_report/uk.xlsx
+++ b/api/templates/genxpert_tb_workload_report/uk.xlsx
@@ -1,20 +1,39 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
-  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10531"/>
+  <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ahernandez/repos/aspect/api/templates/genxpert_tb_workload_report/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7C9E5455-ED50-C44C-A2F2-E8756429D15D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="760" windowWidth="34560" windowHeight="21580"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="34560" windowHeight="21680" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet sheetId="1" name="Пристрої" state="visible" r:id="rId4"/>
+    <sheet name="Devices" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="171027"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="90">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="95" uniqueCount="92">
   <si>
     <t>Пристрої GeneXpert</t>
   </si>
@@ -43,15 +62,18 @@
     <t># Використовувані модулі</t>
   </si>
   <si>
+    <t>Підраховує кількість днів, коли пристрій принаймні один раз повідомлялося про будь-який із статусів неактивності (включно зі статусами «Невідомо» та «Тестування не проводилися»).</t>
+  </si>
+  <si>
     <t>&lt;Table&gt;</t>
   </si>
   <si>
+    <t>пристрій</t>
+  </si>
+  <si>
     <t>Назва сайту</t>
   </si>
   <si>
-    <t>пристрій</t>
-  </si>
-  <si>
     <t>Держава</t>
   </si>
   <si>
@@ -166,12 +188,12 @@
     <t>Реєстраційний номер SIM-карти №2</t>
   </si>
   <si>
+    <t>&lt;name&gt;</t>
+  </si>
+  <si>
     <t>&lt;siteName&gt;</t>
   </si>
   <si>
-    <t>&lt;name&gt;</t>
-  </si>
-  <si>
     <t>&lt;stateName&gt;</t>
   </si>
   <si>
@@ -284,74 +306,71 @@
   </si>
   <si>
     <t>&lt;sim2SerialNumber&gt;</t>
+  </si>
+  <si>
+    <t>&lt;DecommissionedDevicesLabel&gt;: &lt;DecommissionedDevices&gt;</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="yyyy-mm-dd hh:mm"/>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd\ hh:mm"/>
+    <numFmt numFmtId="165" formatCode="[$-409]mmmm\ d\,\ yyyy;@"/>
   </numFmts>
-  <fonts count="9" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
-      <color theme="1"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
+      <sz val="12"/>
       <color indexed="64"/>
-      <sz val="12"/>
       <name val="Calibri"/>
     </font>
     <font>
       <b/>
+      <sz val="16"/>
       <color indexed="64"/>
+      <name val="Calibri"/>
       <family val="2"/>
-      <sz val="16"/>
-      <name val="Calibri"/>
     </font>
     <font>
       <u/>
+      <sz val="12"/>
       <color indexed="64"/>
+      <name val="Calibri"/>
       <family val="2"/>
-      <sz val="12"/>
-      <name val="Calibri"/>
     </font>
     <font>
       <i/>
+      <sz val="12"/>
       <color indexed="64"/>
+      <name val="Calibri"/>
       <family val="2"/>
-      <sz val="12"/>
-      <name val="Calibri"/>
     </font>
     <font>
       <b/>
+      <sz val="12"/>
       <color indexed="64"/>
+      <name val="Calibri"/>
       <family val="2"/>
-      <sz val="12"/>
-      <name val="Calibri"/>
     </font>
     <font>
       <b/>
-      <family val="2"/>
       <sz val="12"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
-      <color indexed="64"/>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
       <family val="2"/>
-      <sz val="12"/>
-      <name val="Calibri"/>
+      <scheme val="minor"/>
     </font>
     <font>
-      <color theme="1"/>
+      <sz val="12"/>
+      <color indexed="64"/>
+      <name val="Calibri"/>
       <family val="2"/>
-      <scheme val="minor"/>
-      <sz val="12"/>
-      <name val="Calibri"/>
     </font>
   </fonts>
   <fills count="3">
@@ -368,7 +387,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="7">
     <border>
       <left/>
       <right/>
@@ -377,77 +396,143 @@
       <diagonal/>
     </border>
     <border>
-      <left style="medium"/>
-      <right style="medium"/>
-      <top style="medium"/>
-      <bottom style="medium"/>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
+      <bottom style="medium">
+        <color auto="1"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top/>
-      <bottom style="thin"/>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
       <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="10" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="5" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="5" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top"/>
+    <xf numFmtId="164" fontId="5" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="10" fontId="5" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="5" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="5" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="6" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="6" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="10" fontId="6" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="14" fontId="7" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="10" fontId="7" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="10" fontId="7" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="14" fontId="8" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="8" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -674,47 +759,38 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:AR14"/>
-  <sheetFormatPr defaultRowHeight="16" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.2" defaultColWidth="11.33203125" customHeight="1"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:AQ14"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.33203125" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="27.1640625" customWidth="1"/>
-    <col min="2" max="2" width="10.83203125" customWidth="1"/>
-    <col min="3" max="3" width="35.33203125" customWidth="1"/>
-    <col min="4" max="4" width="33.5" customWidth="1"/>
-    <col min="5" max="5" width="28.5" customWidth="1"/>
-    <col min="6" max="6" width="15.33203125" customWidth="1"/>
-    <col min="7" max="7" width="17.83203125" customWidth="1"/>
-    <col min="8" max="9" width="11.6640625" customWidth="1"/>
-    <col min="10" max="10" width="12.5" customWidth="1"/>
-    <col min="11" max="11" width="11" customWidth="1"/>
-    <col min="12" max="12" width="12.6640625" customWidth="1"/>
-    <col min="13" max="13" width="13.5" customWidth="1"/>
-    <col min="14" max="14" width="10.83203125" customWidth="1"/>
-    <col min="15" max="15" width="11.33203125" customWidth="1"/>
-    <col min="16" max="16" width="12.83203125" customWidth="1"/>
-    <col min="17" max="22" width="9.5" customWidth="1"/>
-    <col min="23" max="23" width="16" customWidth="1"/>
-    <col min="24" max="24" width="18.83203125" customWidth="1"/>
-    <col min="25" max="26" width="20.6640625" customWidth="1"/>
-    <col min="27" max="27" width="20.6640625" style="1" customWidth="1"/>
-    <col min="28" max="28" width="20.1640625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="30.6640625" customWidth="1"/>
+    <col min="3" max="3" width="40.33203125" customWidth="1"/>
+    <col min="4" max="4" width="42.1640625" customWidth="1"/>
+    <col min="5" max="7" width="15.33203125" customWidth="1"/>
+    <col min="8" max="12" width="11.6640625" customWidth="1"/>
+    <col min="13" max="15" width="15.6640625" customWidth="1"/>
+    <col min="16" max="16" width="13.6640625" customWidth="1"/>
+    <col min="17" max="23" width="15.6640625" customWidth="1"/>
+    <col min="24" max="26" width="20.6640625" customWidth="1"/>
+    <col min="27" max="28" width="20.6640625" style="1" customWidth="1"/>
     <col min="29" max="29" width="33.33203125" customWidth="1"/>
-    <col min="30" max="31" width="25.6640625" customWidth="1"/>
-    <col min="32" max="32" width="17.5" customWidth="1"/>
-    <col min="33" max="33" width="21.1640625" customWidth="1"/>
-    <col min="34" max="34" width="20.6640625" customWidth="1"/>
-    <col min="35" max="35" width="20.33203125" customWidth="1"/>
-    <col min="36" max="36" width="16.83203125" customWidth="1"/>
-    <col min="37" max="37" width="16.6640625" customWidth="1"/>
-    <col min="38" max="38" width="18.1640625" customWidth="1"/>
-    <col min="39" max="39" width="22" customWidth="1"/>
-    <col min="40" max="40" width="24.33203125" customWidth="1"/>
-    <col min="41" max="41" width="16.33203125" customWidth="1"/>
-    <col min="42" max="43" width="29.1640625" customWidth="1"/>
+    <col min="30" max="30" width="32.83203125" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="31.1640625" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="20.6640625" customWidth="1"/>
+    <col min="33" max="33" width="21.1640625" bestFit="1"/>
+    <col min="34" max="34" width="18.83203125" bestFit="1"/>
+    <col min="35" max="35" width="10.1640625" bestFit="1"/>
+    <col min="36" max="36" width="16.5" bestFit="1"/>
+    <col min="37" max="37" width="16.83203125" bestFit="1"/>
+    <col min="38" max="38" width="13" bestFit="1"/>
+    <col min="39" max="39" width="22" bestFit="1"/>
+    <col min="40" max="40" width="24.33203125" bestFit="1"/>
+    <col min="41" max="41" width="14.33203125" bestFit="1"/>
+    <col min="42" max="43" width="29.1640625" bestFit="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="21" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:43" ht="21" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -724,7 +800,7 @@
       <c r="F1" s="2"/>
       <c r="G1" s="2"/>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -732,333 +808,334 @@
         <v>2</v>
       </c>
     </row>
-    <row r="3" ht="16" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>3</v>
       </c>
-      <c r="C3" s="4" t="s">
+      <c r="C3" s="22" t="s">
         <v>4</v>
       </c>
-      <c r="D3" s="4"/>
-      <c r="E3" s="4"/>
-      <c r="F3" s="4"/>
-      <c r="G3" s="4"/>
+      <c r="D3" s="22"/>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="5" ht="17" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A5" s="5" t="s">
+    <row r="5" spans="1:43" ht="17" x14ac:dyDescent="0.2">
+      <c r="A5" s="4" t="s">
         <v>6</v>
       </c>
       <c r="C5" s="3" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="6" ht="47.5" customHeight="1" spans="3:10" x14ac:dyDescent="0.25">
-      <c r="C6" s="6" t="s">
+    <row r="6" spans="1:43" x14ac:dyDescent="0.2">
+      <c r="A6" s="26" t="s">
+        <v>91</v>
+      </c>
+      <c r="C6" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="D6" s="7"/>
-      <c r="E6" s="7"/>
-      <c r="F6" s="7"/>
-      <c r="G6" s="7"/>
-      <c r="H6" s="7"/>
-      <c r="I6" s="7"/>
-      <c r="J6"/>
+      <c r="D6" s="23" t="s">
+        <v>9</v>
+      </c>
+      <c r="E6" s="23"/>
+      <c r="F6" s="23"/>
+      <c r="G6" s="23"/>
+      <c r="H6" s="23"/>
+      <c r="I6" s="23"/>
     </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A7" s="8"/>
+    <row r="7" spans="1:43" x14ac:dyDescent="0.2">
+      <c r="A7" s="6"/>
     </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A8" s="9"/>
+    <row r="8" spans="1:43" x14ac:dyDescent="0.2">
+      <c r="A8" s="7"/>
     </row>
-    <row r="9" ht="17" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:43" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
-    <row r="10" ht="52" customHeight="1" spans="1:44" s="10" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="11" t="s">
-        <v>10</v>
-      </c>
-      <c r="B10" s="11" t="s">
+    <row r="10" spans="1:43" s="8" customFormat="1" ht="52" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="B10" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="C10" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="D10" s="11" t="s">
+      <c r="C10" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="E10" s="11" t="s">
+      <c r="D10" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="F10" s="11" t="s">
+      <c r="E10" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="G10" s="11" t="s">
+      <c r="F10" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="H10" s="11" t="s">
+      <c r="G10" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="I10" s="11" t="s">
+      <c r="H10" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="J10" s="12" t="s">
+      <c r="I10" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="K10" s="12" t="s">
+      <c r="J10" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="L10" s="12" t="s">
+      <c r="K10" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="M10" s="12" t="s">
-        <v>21</v>
-      </c>
-      <c r="N10" s="12" t="s">
+      <c r="L10" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="O10" s="13" t="s">
+      <c r="M10" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="N10" s="10" t="s">
         <v>23</v>
       </c>
-      <c r="P10" s="12" t="s">
+      <c r="O10" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="Q10" s="11" t="s">
+      <c r="P10" s="9" t="s">
         <v>25</v>
       </c>
-      <c r="R10" s="11" t="s">
+      <c r="Q10" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="S10" s="11" t="s">
+      <c r="R10" s="9" t="s">
         <v>27</v>
       </c>
-      <c r="T10" s="11" t="s">
+      <c r="S10" s="9" t="s">
         <v>28</v>
       </c>
-      <c r="U10" s="11" t="s">
+      <c r="T10" s="9" t="s">
         <v>29</v>
       </c>
-      <c r="V10" s="11" t="s">
+      <c r="U10" s="9" t="s">
         <v>30</v>
       </c>
-      <c r="W10" s="12" t="s">
+      <c r="V10" s="9" t="s">
         <v>31</v>
       </c>
-      <c r="X10" s="12" t="s">
+      <c r="W10" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="X10" s="10" t="s">
         <v>8</v>
       </c>
-      <c r="Y10" s="11" t="s">
-        <v>32</v>
+      <c r="Y10" s="9" t="s">
+        <v>33</v>
       </c>
       <c r="Z10" s="11" t="s">
-        <v>32</v>
-      </c>
-      <c r="AA10" s="14" t="s">
         <v>33</v>
       </c>
-      <c r="AB10" s="14" t="s">
+      <c r="AA10" s="12" t="s">
         <v>34</v>
       </c>
-      <c r="AC10" s="11" t="s">
+      <c r="AB10" s="12" t="s">
         <v>35</v>
       </c>
-      <c r="AD10" s="11" t="s">
+      <c r="AC10" s="9" t="s">
         <v>36</v>
       </c>
-      <c r="AE10" s="11" t="s">
+      <c r="AD10" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="AF10" s="11" t="s">
+      <c r="AE10" s="9" t="s">
         <v>38</v>
       </c>
-      <c r="AG10" s="11" t="s">
+      <c r="AF10" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="AH10" s="11" t="s">
+      <c r="AG10" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="AI10" s="11" t="s">
+      <c r="AH10" s="13" t="s">
         <v>41</v>
       </c>
-      <c r="AJ10" s="11" t="s">
+      <c r="AI10" s="13" t="s">
         <v>42</v>
       </c>
-      <c r="AK10" s="11" t="s">
+      <c r="AJ10" s="13" t="s">
         <v>43</v>
       </c>
-      <c r="AL10" s="11" t="s">
+      <c r="AK10" s="13" t="s">
         <v>44</v>
       </c>
-      <c r="AM10" s="11" t="s">
+      <c r="AL10" s="13" t="s">
         <v>45</v>
       </c>
-      <c r="AN10" s="11" t="s">
+      <c r="AM10" s="13" t="s">
         <v>46</v>
       </c>
-      <c r="AO10" s="11" t="s">
+      <c r="AN10" s="13" t="s">
         <v>47</v>
       </c>
-      <c r="AP10" s="11" t="s">
+      <c r="AO10" s="13" t="s">
         <v>48</v>
       </c>
-      <c r="AQ10" s="11" t="s">
+      <c r="AP10" s="13" t="s">
         <v>49</v>
       </c>
+      <c r="AQ10" s="14" t="s">
+        <v>50</v>
+      </c>
     </row>
-    <row r="11" spans="1:44" x14ac:dyDescent="0.25">
-      <c r="A11" s="15" t="s">
-        <v>50</v>
+    <row r="11" spans="1:43" x14ac:dyDescent="0.2">
+      <c r="A11" s="24" t="s">
+        <v>52</v>
       </c>
       <c r="B11" s="15" t="s">
         <v>51</v>
       </c>
       <c r="C11" s="15" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="D11" s="15" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E11" s="15" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F11" s="15" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="G11" s="15" t="s">
-        <v>56</v>
-      </c>
-      <c r="H11" s="16" t="s">
         <v>57</v>
       </c>
-      <c r="I11" s="16" t="s">
+      <c r="H11" s="15" t="s">
         <v>58</v>
       </c>
-      <c r="J11" s="16" t="s">
+      <c r="I11" s="15" t="s">
         <v>59</v>
       </c>
-      <c r="K11" s="16" t="s">
+      <c r="J11" s="15" t="s">
         <v>60</v>
       </c>
-      <c r="L11" s="16" t="s">
+      <c r="K11" s="25" t="s">
         <v>61</v>
       </c>
-      <c r="M11" s="16" t="s">
+      <c r="L11" s="25" t="s">
         <v>62</v>
       </c>
-      <c r="N11" s="16" t="s">
+      <c r="M11" s="25" t="s">
         <v>63</v>
       </c>
-      <c r="O11" s="16" t="s">
+      <c r="N11" s="15" t="s">
         <v>64</v>
       </c>
-      <c r="P11" s="16" t="s">
+      <c r="O11" s="15" t="s">
         <v>65</v>
       </c>
+      <c r="P11" s="15" t="s">
+        <v>66</v>
+      </c>
       <c r="Q11" s="16" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="R11" s="16" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="S11" s="16" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="T11" s="16" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="U11" s="16" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="V11" s="16" t="s">
-        <v>71</v>
-      </c>
-      <c r="W11" s="16" t="s">
         <v>72</v>
       </c>
-      <c r="X11" s="16" t="s">
+      <c r="W11" s="15" t="s">
         <v>73</v>
       </c>
-      <c r="Y11" s="17" t="s">
+      <c r="X11" s="15" t="s">
         <v>74</v>
       </c>
-      <c r="Z11" s="18" t="s">
+      <c r="Y11" s="15" t="s">
         <v>75</v>
       </c>
-      <c r="AA11" s="19" t="e">
-        <f>IF(AG11=0,0,L11/AG11)</f>
+      <c r="Z11" s="15" t="s">
+        <v>76</v>
+      </c>
+      <c r="AA11" s="17" t="e">
+        <f>IF(AF11=0,0,K11/AF11)</f>
         <v>#VALUE!</v>
       </c>
-      <c r="AB11" s="20" t="e">
-        <f>IF(AG11=0,0,(L11+M11)/AG11)</f>
+      <c r="AB11" s="18" t="e">
+        <f>IF(AF11=0,0,(K11+L11)/AF11)</f>
         <v>#VALUE!</v>
       </c>
-      <c r="AC11" s="20" t="e">
-        <f>IF(AC11&gt;0.05,"Високий рівень помилок/недійсних даних. Звертайтесь до лаб.","")</f>
+      <c r="AC11" s="18" t="e">
+        <f>IF(AB11&gt;0.05,"Високий рівень помилок/недійсних даних. Звертайтесь до лаб.","")</f>
         <v>#VALUE!</v>
       </c>
-      <c r="AD11" s="17" t="s">
-        <v>76</v>
-      </c>
-      <c r="AE11" s="17" t="s">
+      <c r="AD11" s="18" t="s">
         <v>77</v>
       </c>
-      <c r="AF11" s="16" t="s">
+      <c r="AE11" s="18" t="s">
         <v>78</v>
       </c>
-      <c r="AG11" s="21" t="s">
+      <c r="AF11" s="15" t="s">
         <v>79</v>
       </c>
-      <c r="AH11" s="22" t="s">
+      <c r="AG11" s="19" t="s">
         <v>80</v>
       </c>
-      <c r="AI11" s="22" t="s">
+      <c r="AH11" s="20" t="s">
         <v>81</v>
       </c>
-      <c r="AJ11" s="22" t="s">
+      <c r="AI11" s="20" t="s">
         <v>82</v>
       </c>
-      <c r="AK11" s="22" t="s">
+      <c r="AJ11" s="20" t="s">
         <v>83</v>
       </c>
-      <c r="AL11" s="22" t="s">
+      <c r="AK11" s="20" t="s">
         <v>84</v>
       </c>
-      <c r="AM11" s="22" t="s">
+      <c r="AL11" s="20" t="s">
         <v>85</v>
       </c>
-      <c r="AN11" s="21" t="s">
+      <c r="AM11" s="20" t="s">
         <v>86</v>
       </c>
-      <c r="AO11" s="23" t="s">
+      <c r="AN11" s="19" t="s">
         <v>87</v>
       </c>
-      <c r="AP11" s="22" t="s">
+      <c r="AO11" s="20" t="s">
         <v>88</v>
       </c>
-      <c r="AQ11" s="22" t="s">
+      <c r="AP11" s="20" t="s">
         <v>89</v>
       </c>
+      <c r="AQ11" s="20" t="s">
+        <v>90</v>
+      </c>
     </row>
-    <row r="14" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B14" s="24"/>
-      <c r="C14" s="24"/>
-      <c r="D14" s="24"/>
-      <c r="E14" s="24"/>
-      <c r="F14" s="24"/>
-      <c r="G14" s="24"/>
+    <row r="14" spans="1:43" x14ac:dyDescent="0.2">
+      <c r="B14" s="21"/>
+      <c r="C14" s="21"/>
+      <c r="D14" s="21"/>
+      <c r="E14" s="21"/>
+      <c r="F14" s="21"/>
+      <c r="G14" s="21"/>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="C3:E3"/>
-    <mergeCell ref="D6:J6"/>
+    <mergeCell ref="C3:D3"/>
+    <mergeCell ref="D6:I6"/>
   </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5118110236220469" footer="0.5118110236220469"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.51181102362204689" footer="0.51181102362204689"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
 </file>
--- a/api/templates/genxpert_tb_workload_report/uk.xlsx
+++ b/api/templates/genxpert_tb_workload_report/uk.xlsx
@@ -1,34 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10531"/>
-  <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ahernandez/repos/aspect/api/templates/genxpert_tb_workload_report/"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7C9E5455-ED50-C44C-A2F2-E8756429D15D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
+  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="34560" windowHeight="21680" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="34560" windowHeight="21680"/>
   </bookViews>
   <sheets>
-    <sheet name="Devices" sheetId="1" r:id="rId1"/>
+    <sheet sheetId="1" name="Devices" state="visible" r:id="rId4"/>
   </sheets>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <calcPr calcId="171027"/>
 </workbook>
 </file>
 
@@ -59,6 +40,9 @@
     <t>Список літератури</t>
   </si>
   <si>
+    <t>&lt;DecommissionedDevicesLabel&gt;: &lt;DecommissionedDevices&gt;</t>
+  </si>
+  <si>
     <t># Використовувані модулі</t>
   </si>
   <si>
@@ -68,12 +52,12 @@
     <t>&lt;Table&gt;</t>
   </si>
   <si>
+    <t>Назва сайту</t>
+  </si>
+  <si>
     <t>пристрій</t>
   </si>
   <si>
-    <t>Назва сайту</t>
-  </si>
-  <si>
     <t>Держава</t>
   </si>
   <si>
@@ -188,12 +172,12 @@
     <t>Реєстраційний номер SIM-карти №2</t>
   </si>
   <si>
+    <t>&lt;siteName&gt;</t>
+  </si>
+  <si>
     <t>&lt;name&gt;</t>
   </si>
   <si>
-    <t>&lt;siteName&gt;</t>
-  </si>
-  <si>
     <t>&lt;stateName&gt;</t>
   </si>
   <si>
@@ -306,71 +290,75 @@
   </si>
   <si>
     <t>&lt;sim2SerialNumber&gt;</t>
-  </si>
-  <si>
-    <t>&lt;DecommissionedDevicesLabel&gt;: &lt;DecommissionedDevices&gt;</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd\ hh:mm"/>
-    <numFmt numFmtId="165" formatCode="[$-409]mmmm\ d\,\ yyyy;@"/>
+    <numFmt numFmtId="164" formatCode="yyyy-mm-dd hh:mm"/>
+    <numFmt numFmtId="165" formatCode="[$-409]mmmm d, yyyy;@"/>
   </numFmts>
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
+      <color theme="1"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <color indexed="64"/>
       <sz val="12"/>
-      <color indexed="64"/>
       <name val="Calibri"/>
     </font>
     <font>
       <b/>
+      <color indexed="64"/>
+      <family val="2"/>
       <sz val="16"/>
-      <color indexed="64"/>
       <name val="Calibri"/>
-      <family val="2"/>
     </font>
     <font>
       <u/>
+      <color indexed="64"/>
+      <family val="2"/>
       <sz val="12"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
       <color indexed="64"/>
+      <family val="2"/>
+      <sz val="12"/>
       <name val="Calibri"/>
-      <family val="2"/>
     </font>
     <font>
       <i/>
+      <color indexed="64"/>
+      <family val="2"/>
       <sz val="12"/>
-      <color indexed="64"/>
       <name val="Calibri"/>
-      <family val="2"/>
     </font>
     <font>
       <b/>
+      <color indexed="64"/>
+      <family val="2"/>
       <sz val="12"/>
-      <color indexed="64"/>
       <name val="Calibri"/>
-      <family val="2"/>
     </font>
     <font>
       <b/>
+      <family val="2"/>
       <sz val="12"/>
       <name val="Calibri"/>
-      <family val="2"/>
     </font>
     <font>
-      <sz val="12"/>
       <color theme="1"/>
-      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="12"/>
-      <color indexed="64"/>
       <name val="Calibri"/>
-      <family val="2"/>
     </font>
   </fonts>
   <fills count="3">
@@ -396,87 +384,45 @@
       <diagonal/>
     </border>
     <border>
-      <left style="medium">
-        <color auto="1"/>
-      </left>
-      <right style="medium">
-        <color auto="1"/>
-      </right>
-      <top style="medium">
-        <color auto="1"/>
-      </top>
-      <bottom style="medium">
-        <color auto="1"/>
-      </bottom>
+      <left style="medium"/>
+      <right style="medium"/>
+      <top style="medium"/>
+      <bottom style="medium"/>
       <diagonal/>
     </border>
     <border>
-      <left style="medium">
-        <color auto="1"/>
-      </left>
-      <right style="medium">
-        <color auto="1"/>
-      </right>
-      <top style="medium">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
+      <left style="medium"/>
+      <right style="medium"/>
+      <top style="medium"/>
+      <bottom style="thin"/>
       <diagonal/>
     </border>
     <border>
-      <left style="medium">
-        <color auto="1"/>
-      </left>
-      <right style="medium">
-        <color auto="1"/>
-      </right>
-      <top style="medium">
-        <color auto="1"/>
-      </top>
+      <left style="medium"/>
+      <right style="medium"/>
+      <top style="medium"/>
       <bottom/>
       <diagonal/>
     </border>
     <border>
-      <left style="medium">
-        <color auto="1"/>
-      </left>
+      <left style="medium"/>
       <right/>
-      <top style="medium">
-        <color auto="1"/>
-      </top>
+      <top style="medium"/>
       <bottom/>
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="medium">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="medium"/>
+      <bottom style="thin"/>
       <diagonal/>
     </border>
   </borders>
@@ -485,54 +431,54 @@
   </cellStyleXfs>
   <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="10" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="5" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="7" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="7" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="10" fontId="5" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="5" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="5" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="164" fontId="7" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="10" fontId="7" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="7" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="7" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="10" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="6" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="10" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="10" fontId="1" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="8" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -759,9 +705,9 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:AQ14"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.33203125" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="16" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.2" defaultColWidth="11.33203125" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="27.1640625" customWidth="1"/>
     <col min="2" max="2" width="30.6640625" customWidth="1"/>
@@ -775,22 +721,22 @@
     <col min="24" max="26" width="20.6640625" customWidth="1"/>
     <col min="27" max="28" width="20.6640625" style="1" customWidth="1"/>
     <col min="29" max="29" width="33.33203125" customWidth="1"/>
-    <col min="30" max="30" width="32.83203125" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="31.1640625" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="32.83203125" customWidth="1"/>
+    <col min="31" max="31" width="31.1640625" customWidth="1"/>
     <col min="32" max="32" width="20.6640625" customWidth="1"/>
-    <col min="33" max="33" width="21.1640625" bestFit="1"/>
-    <col min="34" max="34" width="18.83203125" bestFit="1"/>
-    <col min="35" max="35" width="10.1640625" bestFit="1"/>
-    <col min="36" max="36" width="16.5" bestFit="1"/>
-    <col min="37" max="37" width="16.83203125" bestFit="1"/>
-    <col min="38" max="38" width="13" bestFit="1"/>
-    <col min="39" max="39" width="22" bestFit="1"/>
-    <col min="40" max="40" width="24.33203125" bestFit="1"/>
-    <col min="41" max="41" width="14.33203125" bestFit="1"/>
-    <col min="42" max="43" width="29.1640625" bestFit="1"/>
+    <col min="33" max="33" width="21.1640625" customWidth="1"/>
+    <col min="34" max="34" width="18.83203125" customWidth="1"/>
+    <col min="35" max="35" width="10.1640625" customWidth="1"/>
+    <col min="36" max="36" width="16.5" customWidth="1"/>
+    <col min="37" max="37" width="16.83203125" customWidth="1"/>
+    <col min="38" max="38" width="13" customWidth="1"/>
+    <col min="39" max="39" width="22" customWidth="1"/>
+    <col min="40" max="40" width="24.33203125" customWidth="1"/>
+    <col min="41" max="41" width="14.33203125" customWidth="1"/>
+    <col min="42" max="43" width="29.1640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:43" ht="21" x14ac:dyDescent="0.25">
+    <row r="1" ht="21" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -800,7 +746,7 @@
       <c r="F1" s="2"/>
       <c r="G1" s="2"/>
     </row>
-    <row r="2" spans="1:43" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -808,334 +754,334 @@
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="1:43" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>3</v>
       </c>
-      <c r="C3" s="22" t="s">
+      <c r="C3" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="D3" s="22"/>
-    </row>
-    <row r="4" spans="1:43" x14ac:dyDescent="0.2">
+      <c r="D3" s="4"/>
+    </row>
+    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="5" spans="1:43" ht="17" x14ac:dyDescent="0.2">
-      <c r="A5" s="4" t="s">
+    <row r="5" ht="17" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C5" s="3" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="6" spans="1:43" x14ac:dyDescent="0.2">
-      <c r="A6" s="26" t="s">
-        <v>91</v>
-      </c>
-      <c r="C6" s="5" t="s">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A6" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="D6" s="23" t="s">
+      <c r="C6" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="E6" s="23"/>
-      <c r="F6" s="23"/>
-      <c r="G6" s="23"/>
-      <c r="H6" s="23"/>
-      <c r="I6" s="23"/>
-    </row>
-    <row r="7" spans="1:43" x14ac:dyDescent="0.2">
-      <c r="A7" s="6"/>
-    </row>
-    <row r="8" spans="1:43" x14ac:dyDescent="0.2">
-      <c r="A8" s="7"/>
-    </row>
-    <row r="9" spans="1:43" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="D6" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="E6" s="8"/>
+      <c r="F6" s="8"/>
+      <c r="G6" s="8"/>
+      <c r="H6" s="8"/>
+      <c r="I6" s="8"/>
+    </row>
+    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A7" s="9"/>
+    </row>
+    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A8" s="10"/>
+    </row>
+    <row r="9" ht="17" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="10" spans="1:43" s="8" customFormat="1" ht="52" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="9" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="10" ht="52" customHeight="1" spans="1:43" s="11" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="12" t="s">
         <v>12</v>
       </c>
-      <c r="B10" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="C10" s="9" t="s">
+      <c r="B10" s="12" t="s">
         <v>13</v>
       </c>
-      <c r="D10" s="9" t="s">
+      <c r="C10" s="12" t="s">
         <v>14</v>
       </c>
-      <c r="E10" s="9" t="s">
+      <c r="D10" s="12" t="s">
         <v>15</v>
       </c>
-      <c r="F10" s="9" t="s">
+      <c r="E10" s="12" t="s">
         <v>16</v>
       </c>
-      <c r="G10" s="9" t="s">
+      <c r="F10" s="12" t="s">
         <v>17</v>
       </c>
-      <c r="H10" s="9" t="s">
+      <c r="G10" s="12" t="s">
         <v>18</v>
       </c>
-      <c r="I10" s="9" t="s">
+      <c r="H10" s="12" t="s">
         <v>19</v>
       </c>
-      <c r="J10" s="9" t="s">
+      <c r="I10" s="12" t="s">
         <v>20</v>
       </c>
-      <c r="K10" s="9" t="s">
+      <c r="J10" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="L10" s="9" t="s">
+      <c r="K10" s="12" t="s">
         <v>22</v>
       </c>
-      <c r="M10" s="9" t="s">
-        <v>22</v>
-      </c>
-      <c r="N10" s="10" t="s">
+      <c r="L10" s="12" t="s">
         <v>23</v>
       </c>
-      <c r="O10" s="10" t="s">
+      <c r="M10" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="N10" s="13" t="s">
         <v>24</v>
       </c>
-      <c r="P10" s="9" t="s">
+      <c r="O10" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="Q10" s="9" t="s">
+      <c r="P10" s="12" t="s">
         <v>26</v>
       </c>
-      <c r="R10" s="9" t="s">
+      <c r="Q10" s="12" t="s">
         <v>27</v>
       </c>
-      <c r="S10" s="9" t="s">
+      <c r="R10" s="12" t="s">
         <v>28</v>
       </c>
-      <c r="T10" s="9" t="s">
+      <c r="S10" s="12" t="s">
         <v>29</v>
       </c>
-      <c r="U10" s="9" t="s">
+      <c r="T10" s="12" t="s">
         <v>30</v>
       </c>
-      <c r="V10" s="9" t="s">
+      <c r="U10" s="12" t="s">
         <v>31</v>
       </c>
-      <c r="W10" s="10" t="s">
+      <c r="V10" s="12" t="s">
         <v>32</v>
       </c>
-      <c r="X10" s="10" t="s">
-        <v>8</v>
-      </c>
-      <c r="Y10" s="9" t="s">
+      <c r="W10" s="13" t="s">
         <v>33</v>
       </c>
-      <c r="Z10" s="11" t="s">
-        <v>33</v>
-      </c>
-      <c r="AA10" s="12" t="s">
+      <c r="X10" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="Y10" s="12" t="s">
         <v>34</v>
       </c>
-      <c r="AB10" s="12" t="s">
+      <c r="Z10" s="14" t="s">
+        <v>34</v>
+      </c>
+      <c r="AA10" s="15" t="s">
         <v>35</v>
       </c>
-      <c r="AC10" s="9" t="s">
+      <c r="AB10" s="15" t="s">
         <v>36</v>
       </c>
-      <c r="AD10" s="9" t="s">
+      <c r="AC10" s="12" t="s">
         <v>37</v>
       </c>
-      <c r="AE10" s="9" t="s">
+      <c r="AD10" s="12" t="s">
         <v>38</v>
       </c>
-      <c r="AF10" s="9" t="s">
+      <c r="AE10" s="12" t="s">
         <v>39</v>
       </c>
-      <c r="AG10" s="13" t="s">
+      <c r="AF10" s="12" t="s">
         <v>40</v>
       </c>
-      <c r="AH10" s="13" t="s">
+      <c r="AG10" s="16" t="s">
         <v>41</v>
       </c>
-      <c r="AI10" s="13" t="s">
+      <c r="AH10" s="16" t="s">
         <v>42</v>
       </c>
-      <c r="AJ10" s="13" t="s">
+      <c r="AI10" s="16" t="s">
         <v>43</v>
       </c>
-      <c r="AK10" s="13" t="s">
+      <c r="AJ10" s="16" t="s">
         <v>44</v>
       </c>
-      <c r="AL10" s="13" t="s">
+      <c r="AK10" s="16" t="s">
         <v>45</v>
       </c>
-      <c r="AM10" s="13" t="s">
+      <c r="AL10" s="16" t="s">
         <v>46</v>
       </c>
-      <c r="AN10" s="13" t="s">
+      <c r="AM10" s="16" t="s">
         <v>47</v>
       </c>
-      <c r="AO10" s="13" t="s">
+      <c r="AN10" s="16" t="s">
         <v>48</v>
       </c>
-      <c r="AP10" s="13" t="s">
+      <c r="AO10" s="16" t="s">
         <v>49</v>
       </c>
-      <c r="AQ10" s="14" t="s">
+      <c r="AP10" s="16" t="s">
         <v>50</v>
       </c>
-    </row>
-    <row r="11" spans="1:43" x14ac:dyDescent="0.2">
-      <c r="A11" s="24" t="s">
+      <c r="AQ10" s="17" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="11" spans="1:43" x14ac:dyDescent="0.25">
+      <c r="A11" s="18" t="s">
         <v>52</v>
       </c>
-      <c r="B11" s="15" t="s">
-        <v>51</v>
-      </c>
-      <c r="C11" s="15" t="s">
+      <c r="B11" s="19" t="s">
         <v>53</v>
       </c>
-      <c r="D11" s="15" t="s">
+      <c r="C11" s="19" t="s">
         <v>54</v>
       </c>
-      <c r="E11" s="15" t="s">
+      <c r="D11" s="19" t="s">
         <v>55</v>
       </c>
-      <c r="F11" s="15" t="s">
+      <c r="E11" s="19" t="s">
         <v>56</v>
       </c>
-      <c r="G11" s="15" t="s">
+      <c r="F11" s="19" t="s">
         <v>57</v>
       </c>
-      <c r="H11" s="15" t="s">
+      <c r="G11" s="19" t="s">
         <v>58</v>
       </c>
-      <c r="I11" s="15" t="s">
+      <c r="H11" s="19" t="s">
         <v>59</v>
       </c>
-      <c r="J11" s="15" t="s">
+      <c r="I11" s="19" t="s">
         <v>60</v>
       </c>
-      <c r="K11" s="25" t="s">
+      <c r="J11" s="19" t="s">
         <v>61</v>
       </c>
-      <c r="L11" s="25" t="s">
+      <c r="K11" s="20" t="s">
         <v>62</v>
       </c>
-      <c r="M11" s="25" t="s">
+      <c r="L11" s="20" t="s">
         <v>63</v>
       </c>
-      <c r="N11" s="15" t="s">
+      <c r="M11" s="20" t="s">
         <v>64</v>
       </c>
-      <c r="O11" s="15" t="s">
+      <c r="N11" s="19" t="s">
         <v>65</v>
       </c>
-      <c r="P11" s="15" t="s">
+      <c r="O11" s="19" t="s">
         <v>66</v>
       </c>
-      <c r="Q11" s="16" t="s">
+      <c r="P11" s="19" t="s">
         <v>67</v>
       </c>
-      <c r="R11" s="16" t="s">
+      <c r="Q11" s="21" t="s">
         <v>68</v>
       </c>
-      <c r="S11" s="16" t="s">
+      <c r="R11" s="21" t="s">
         <v>69</v>
       </c>
-      <c r="T11" s="16" t="s">
+      <c r="S11" s="21" t="s">
         <v>70</v>
       </c>
-      <c r="U11" s="16" t="s">
+      <c r="T11" s="21" t="s">
         <v>71</v>
       </c>
-      <c r="V11" s="16" t="s">
+      <c r="U11" s="21" t="s">
         <v>72</v>
       </c>
-      <c r="W11" s="15" t="s">
+      <c r="V11" s="21" t="s">
         <v>73</v>
       </c>
-      <c r="X11" s="15" t="s">
+      <c r="W11" s="19" t="s">
         <v>74</v>
       </c>
-      <c r="Y11" s="15" t="s">
+      <c r="X11" s="19" t="s">
         <v>75</v>
       </c>
-      <c r="Z11" s="15" t="s">
+      <c r="Y11" s="19" t="s">
         <v>76</v>
       </c>
-      <c r="AA11" s="17" t="e">
+      <c r="Z11" s="19" t="s">
+        <v>77</v>
+      </c>
+      <c r="AA11" s="22" t="e">
         <f>IF(AF11=0,0,K11/AF11)</f>
         <v>#VALUE!</v>
       </c>
-      <c r="AB11" s="18" t="e">
+      <c r="AB11" s="23" t="e">
         <f>IF(AF11=0,0,(K11+L11)/AF11)</f>
         <v>#VALUE!</v>
       </c>
-      <c r="AC11" s="18" t="e">
+      <c r="AC11" s="23" t="e">
         <f>IF(AB11&gt;0.05,"Високий рівень помилок/недійсних даних. Звертайтесь до лаб.","")</f>
         <v>#VALUE!</v>
       </c>
-      <c r="AD11" s="18" t="s">
-        <v>77</v>
-      </c>
-      <c r="AE11" s="18" t="s">
+      <c r="AD11" s="23" t="s">
         <v>78</v>
       </c>
-      <c r="AF11" s="15" t="s">
+      <c r="AE11" s="23" t="s">
         <v>79</v>
       </c>
-      <c r="AG11" s="19" t="s">
+      <c r="AF11" s="19" t="s">
         <v>80</v>
       </c>
-      <c r="AH11" s="20" t="s">
+      <c r="AG11" s="24" t="s">
         <v>81</v>
       </c>
-      <c r="AI11" s="20" t="s">
+      <c r="AH11" s="25" t="s">
         <v>82</v>
       </c>
-      <c r="AJ11" s="20" t="s">
+      <c r="AI11" s="25" t="s">
         <v>83</v>
       </c>
-      <c r="AK11" s="20" t="s">
+      <c r="AJ11" s="25" t="s">
         <v>84</v>
       </c>
-      <c r="AL11" s="20" t="s">
+      <c r="AK11" s="25" t="s">
         <v>85</v>
       </c>
-      <c r="AM11" s="20" t="s">
+      <c r="AL11" s="25" t="s">
         <v>86</v>
       </c>
-      <c r="AN11" s="19" t="s">
+      <c r="AM11" s="25" t="s">
         <v>87</v>
       </c>
-      <c r="AO11" s="20" t="s">
+      <c r="AN11" s="24" t="s">
         <v>88</v>
       </c>
-      <c r="AP11" s="20" t="s">
+      <c r="AO11" s="25" t="s">
         <v>89</v>
       </c>
-      <c r="AQ11" s="20" t="s">
+      <c r="AP11" s="25" t="s">
         <v>90</v>
       </c>
-    </row>
-    <row r="14" spans="1:43" x14ac:dyDescent="0.2">
-      <c r="B14" s="21"/>
-      <c r="C14" s="21"/>
-      <c r="D14" s="21"/>
-      <c r="E14" s="21"/>
-      <c r="F14" s="21"/>
-      <c r="G14" s="21"/>
+      <c r="AQ11" s="25" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="14" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B14" s="26"/>
+      <c r="C14" s="26"/>
+      <c r="D14" s="26"/>
+      <c r="E14" s="26"/>
+      <c r="F14" s="26"/>
+      <c r="G14" s="26"/>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="C3:D3"/>
     <mergeCell ref="D6:I6"/>
   </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.51181102362204689" footer="0.51181102362204689"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5118110236220469" footer="0.5118110236220469"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
 </file>
--- a/api/templates/genxpert_tb_workload_report/uk.xlsx
+++ b/api/templates/genxpert_tb_workload_report/uk.xlsx
@@ -40,7 +40,7 @@
     <t>Список літератури</t>
   </si>
   <si>
-    <t>&lt;DecommissionedDevicesLabel&gt;: &lt;DecommissionedDevices&gt;</t>
+    <t>Виведені з експлуатації пристрої: &lt;DecommissionedDevices&gt;</t>
   </si>
   <si>
     <t># Використовувані модулі</t>
@@ -438,7 +438,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
